--- a/合同全生命周期管理系统-项目管理套件/05_成本与合同管理/成本与合同管理-20260918-V5.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/05_成本与合同管理/成本与合同管理-20260918-V5.xlsx
@@ -125,10 +125,9 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="宋体-简"/>
+      <name val="Carlito"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF008000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -1154,28 +1153,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="10" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="14" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1286,6 +1279,9 @@
     <xf numFmtId="166" fontId="12" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="165" fontId="11" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment vertical="center"/>
     </xf>
@@ -1301,6 +1297,7 @@
     <xf numFmtId="166" fontId="11" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1890,42 +1887,42 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="65" t="inlineStr">
+      <c r="A4" s="63" t="inlineStr">
         <is>
           <t>已量化人工预算</t>
         </is>
       </c>
-      <c r="B4" s="65" t="n"/>
-      <c r="C4" s="65" t="inlineStr">
+      <c r="B4" s="63" t="n"/>
+      <c r="C4" s="63" t="inlineStr">
         <is>
           <t>计划人天</t>
         </is>
       </c>
-      <c r="D4" s="65" t="n"/>
-      <c r="E4" s="65" t="inlineStr">
+      <c r="D4" s="63" t="n"/>
+      <c r="E4" s="63" t="inlineStr">
         <is>
           <t>人日单价</t>
         </is>
       </c>
-      <c r="F4" s="65" t="n"/>
-      <c r="G4" s="65" t="inlineStr">
+      <c r="F4" s="63" t="n"/>
+      <c r="G4" s="63" t="inlineStr">
         <is>
           <t>待估算采购包</t>
         </is>
       </c>
-      <c r="H4" s="65" t="n"/>
-      <c r="I4" s="65" t="inlineStr">
+      <c r="H4" s="63" t="n"/>
+      <c r="I4" s="63" t="inlineStr">
         <is>
           <t>已签合同数</t>
         </is>
       </c>
-      <c r="J4" s="65" t="n"/>
-      <c r="K4" s="65" t="inlineStr">
+      <c r="J4" s="63" t="n"/>
+      <c r="K4" s="63" t="inlineStr">
         <is>
           <t>已付款金额</t>
         </is>
       </c>
-      <c r="L4" s="65" t="n"/>
+      <c r="L4" s="63" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="15">
@@ -1951,22 +1948,22 @@
         <v>0</v>
       </c>
       <c r="J5" s="13" t="n"/>
-      <c r="K5" s="73" t="n">
+      <c r="K5" s="71" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="13" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="66" t="inlineStr">
+      <c r="A8" s="64" t="inlineStr">
         <is>
           <t>预算与合同控制门禁</t>
         </is>
       </c>
-      <c r="B8" s="67" t="n"/>
-      <c r="C8" s="67" t="n"/>
-      <c r="D8" s="67" t="n"/>
-      <c r="E8" s="67" t="n"/>
-      <c r="F8" s="68" t="n"/>
+      <c r="B8" s="65" t="n"/>
+      <c r="C8" s="65" t="n"/>
+      <c r="D8" s="65" t="n"/>
+      <c r="E8" s="65" t="n"/>
+      <c r="F8" s="66" t="n"/>
     </row>
     <row r="9" ht="32" customHeight="1" s="1">
       <c r="A9" s="12" t="inlineStr">
@@ -2006,7 +2003,7 @@
           <t>项目总预算批准</t>
         </is>
       </c>
-      <c r="B10" s="69" t="inlineStr">
+      <c r="B10" s="67" t="inlineStr">
         <is>
           <t>未通过</t>
         </is>
@@ -2016,7 +2013,7 @@
           <t>项目集经理</t>
         </is>
       </c>
-      <c r="D10" s="74" t="n">
+      <c r="D10" s="72" t="n">
         <v>46311</v>
       </c>
       <c r="E10" s="34" t="inlineStr">
@@ -2036,7 +2033,7 @@
           <t>采购包预算完成</t>
         </is>
       </c>
-      <c r="B11" s="69" t="inlineStr">
+      <c r="B11" s="67" t="inlineStr">
         <is>
           <t>未通过</t>
         </is>
@@ -2046,7 +2043,7 @@
           <t>项目经理</t>
         </is>
       </c>
-      <c r="D11" s="74" t="n">
+      <c r="D11" s="72" t="n">
         <v>46310</v>
       </c>
       <c r="E11" s="34" t="inlineStr">
@@ -2066,7 +2063,7 @@
           <t>合同与需求基线一致</t>
         </is>
       </c>
-      <c r="B12" s="69" t="inlineStr">
+      <c r="B12" s="67" t="inlineStr">
         <is>
           <t>未通过</t>
         </is>
@@ -2076,7 +2073,7 @@
           <t>项目经理</t>
         </is>
       </c>
-      <c r="D12" s="74" t="n">
+      <c r="D12" s="72" t="n">
         <v>46326</v>
       </c>
       <c r="E12" s="34" t="inlineStr">
@@ -2096,7 +2093,7 @@
           <t>付款与验收挂钩</t>
         </is>
       </c>
-      <c r="B13" s="69" t="inlineStr">
+      <c r="B13" s="67" t="inlineStr">
         <is>
           <t>未通过</t>
         </is>
@@ -2106,7 +2103,7 @@
           <t>项目经理</t>
         </is>
       </c>
-      <c r="D13" s="74" t="n">
+      <c r="D13" s="72" t="n">
         <v>46326</v>
       </c>
       <c r="E13" s="34" t="inlineStr">
@@ -2126,7 +2123,7 @@
           <t>成本变更纳入控制</t>
         </is>
       </c>
-      <c r="B14" s="69" t="inlineStr">
+      <c r="B14" s="67" t="inlineStr">
         <is>
           <t>未通过</t>
         </is>
@@ -2136,7 +2133,7 @@
           <t>项目集经理</t>
         </is>
       </c>
-      <c r="D14" s="74" t="n">
+      <c r="D14" s="72" t="n">
         <v>46315</v>
       </c>
       <c r="E14" s="34" t="inlineStr">
@@ -2156,7 +2153,7 @@
           <t>成本偏差定期复核</t>
         </is>
       </c>
-      <c r="B15" s="69" t="inlineStr">
+      <c r="B15" s="67" t="inlineStr">
         <is>
           <t>未通过</t>
         </is>
@@ -2166,7 +2163,7 @@
           <t>项目经理</t>
         </is>
       </c>
-      <c r="D15" s="74" t="n">
+      <c r="D15" s="72" t="n">
         <v>46356</v>
       </c>
       <c r="E15" s="34" t="inlineStr">
@@ -2181,16 +2178,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="66" t="inlineStr">
+      <c r="A18" s="64" t="inlineStr">
         <is>
           <t>当前判断</t>
         </is>
       </c>
-      <c r="B18" s="67" t="n"/>
-      <c r="C18" s="67" t="n"/>
-      <c r="D18" s="67" t="n"/>
-      <c r="E18" s="67" t="n"/>
-      <c r="F18" s="68" t="n"/>
+      <c r="B18" s="65" t="n"/>
+      <c r="C18" s="65" t="n"/>
+      <c r="D18" s="65" t="n"/>
+      <c r="E18" s="65" t="n"/>
+      <c r="F18" s="66" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="34" t="inlineStr">
@@ -2198,13 +2195,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B19" s="70" t="inlineStr">
+      <c r="B19" s="68" t="inlineStr">
         <is>
           <t>当前只能确认人工成本769.77万元（5,433人天，按角色×月份月度投入明细汇总），不能把该金额视为项目总预算。</t>
         </is>
       </c>
-      <c r="C19" s="71" t="n"/>
-      <c r="D19" s="72" t="n"/>
+      <c r="C19" s="69" t="n"/>
+      <c r="D19" s="70" t="n"/>
       <c r="E19" s="34" t="n"/>
       <c r="F19" s="34" t="n"/>
     </row>
@@ -2214,13 +2211,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B20" s="70" t="inlineStr">
+      <c r="B20" s="68" t="inlineStr">
         <is>
           <t>CA、电子文档和BI产品应在POC结论后形成许可、实施、接口和运维全口径报价。</t>
         </is>
       </c>
-      <c r="C20" s="71" t="n"/>
-      <c r="D20" s="72" t="n"/>
+      <c r="C20" s="69" t="n"/>
+      <c r="D20" s="70" t="n"/>
       <c r="E20" s="34" t="n"/>
       <c r="F20" s="34" t="n"/>
     </row>
@@ -2230,13 +2227,13 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B21" s="70" t="inlineStr">
+      <c r="B21" s="68" t="inlineStr">
         <is>
           <t>合同付款节点应绑定交付物与验收证据，避免仅按日期或工作量付款。</t>
         </is>
       </c>
-      <c r="C21" s="71" t="n"/>
-      <c r="D21" s="72" t="n"/>
+      <c r="C21" s="69" t="n"/>
+      <c r="D21" s="70" t="n"/>
       <c r="E21" s="34" t="n"/>
       <c r="F21" s="34" t="n"/>
     </row>
@@ -2246,13 +2243,13 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B22" s="70" t="inlineStr">
+      <c r="B22" s="68" t="inlineStr">
         <is>
           <t>新增范围应同时评估人工、采购、进度和后续运维成本，并更新成本基线。</t>
         </is>
       </c>
-      <c r="C22" s="71" t="n"/>
-      <c r="D22" s="72" t="n"/>
+      <c r="C22" s="69" t="n"/>
+      <c r="D22" s="70" t="n"/>
       <c r="E22" s="34" t="n"/>
       <c r="F22" s="34" t="n"/>
     </row>
@@ -2427,7 +2424,7 @@
           <t>正式启动日期</t>
         </is>
       </c>
-      <c r="B13" s="74" t="n">
+      <c r="B13" s="72" t="n">
         <v>46315</v>
       </c>
     </row>
@@ -2437,7 +2434,7 @@
           <t>计划上线日期</t>
         </is>
       </c>
-      <c r="B14" s="74" t="n">
+      <c r="B14" s="72" t="n">
         <v>46538</v>
       </c>
     </row>
@@ -2798,7 +2795,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>角色×月份计划投入人天的唯一录入来源（项目团队按月维护，已含2027-08）；人工成本预算 D 列引用本表合计列，预算人天/差异列为自动核对</t>
+          <t>角色×月份计划/实际投入人天的唯一录入来源（项目团队按月维护，已含2027-08）；人工成本预算 D 列引用本表计划合计列，预算人天列自动核对；差异列为计划-实际进度偏差，完成率=实际/计划</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -3196,22 +3193,22 @@
         <f>人工成本预算!D15&amp;"人天"</f>
         <v>4973人天</v>
       </c>
-      <c r="F5" s="58">
+      <c r="F5" s="56">
         <f>人工成本预算!D15</f>
         <v>4973</v>
       </c>
-      <c r="G5" s="75">
+      <c r="G5" s="73">
         <f>人工成本预算!E3</f>
         <v>1392.43917152624</v>
       </c>
-      <c r="H5" s="76">
+      <c r="H5" s="74">
         <f>F5*G5</f>
         <v>6924600</v>
       </c>
-      <c r="I5" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="61">
+      <c r="I5" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="59">
         <f>IF(H5="","",H5+I5)</f>
         <v>6924600</v>
       </c>
@@ -3258,15 +3255,15 @@
         </is>
       </c>
       <c r="F6" s="24" t="n"/>
-      <c r="G6" s="77" t="n"/>
-      <c r="H6" s="78">
+      <c r="G6" s="75" t="n"/>
+      <c r="H6" s="76">
         <f>F6*G6</f>
         <v>0</v>
       </c>
-      <c r="I6" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="73">
+      <c r="I6" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="71">
         <f>IF(H6="","",H6+I6)</f>
         <v>0</v>
       </c>
@@ -3313,15 +3310,15 @@
         </is>
       </c>
       <c r="F7" s="24" t="n"/>
-      <c r="G7" s="77" t="n"/>
-      <c r="H7" s="78">
+      <c r="G7" s="75" t="n"/>
+      <c r="H7" s="76">
         <f>F7*G7</f>
         <v>0</v>
       </c>
-      <c r="I7" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="73">
+      <c r="I7" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="71">
         <f>IF(H7="","",H7+I7)</f>
         <v>0</v>
       </c>
@@ -3368,15 +3365,15 @@
         </is>
       </c>
       <c r="F8" s="24" t="n"/>
-      <c r="G8" s="77" t="n"/>
-      <c r="H8" s="78">
+      <c r="G8" s="75" t="n"/>
+      <c r="H8" s="76">
         <f>F8*G8</f>
         <v>0</v>
       </c>
-      <c r="I8" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="73">
+      <c r="I8" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="71">
         <f>IF(H8="","",H8+I8)</f>
         <v>0</v>
       </c>
@@ -3423,15 +3420,15 @@
         </is>
       </c>
       <c r="F9" s="24" t="n"/>
-      <c r="G9" s="77" t="n"/>
-      <c r="H9" s="78">
+      <c r="G9" s="75" t="n"/>
+      <c r="H9" s="76">
         <f>F9*G9</f>
         <v>0</v>
       </c>
-      <c r="I9" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="73">
+      <c r="I9" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="71">
         <f>IF(H9="","",H9+I9)</f>
         <v>0</v>
       </c>
@@ -3478,15 +3475,15 @@
         </is>
       </c>
       <c r="F10" s="24" t="n"/>
-      <c r="G10" s="77" t="n"/>
-      <c r="H10" s="78">
+      <c r="G10" s="75" t="n"/>
+      <c r="H10" s="76">
         <f>F10*G10</f>
         <v>0</v>
       </c>
-      <c r="I10" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="73">
+      <c r="I10" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="71">
         <f>IF(H10="","",H10+I10)</f>
         <v>0</v>
       </c>
@@ -3533,15 +3530,15 @@
         </is>
       </c>
       <c r="F11" s="24" t="n"/>
-      <c r="G11" s="77" t="n"/>
-      <c r="H11" s="78">
+      <c r="G11" s="75" t="n"/>
+      <c r="H11" s="76">
         <f>F11*G11</f>
         <v>0</v>
       </c>
-      <c r="I11" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="73">
+      <c r="I11" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="71">
         <f>IF(H11="","",H11+I11)</f>
         <v>0</v>
       </c>
@@ -3588,15 +3585,15 @@
         </is>
       </c>
       <c r="F12" s="24" t="n"/>
-      <c r="G12" s="77" t="n"/>
-      <c r="H12" s="78">
+      <c r="G12" s="75" t="n"/>
+      <c r="H12" s="76">
         <f>F12*G12</f>
         <v>0</v>
       </c>
-      <c r="I12" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="73">
+      <c r="I12" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="71">
         <f>IF(H12="","",H12+I12)</f>
         <v>0</v>
       </c>
@@ -3643,15 +3640,15 @@
         </is>
       </c>
       <c r="F13" s="24" t="n"/>
-      <c r="G13" s="77" t="n"/>
-      <c r="H13" s="78">
+      <c r="G13" s="75" t="n"/>
+      <c r="H13" s="76">
         <f>H5*15%</f>
         <v>1038690</v>
       </c>
-      <c r="I13" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="73">
+      <c r="I13" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="71">
         <f>IF(H13="","",H13+I13)</f>
         <v>1038690</v>
       </c>
@@ -3698,15 +3695,15 @@
         </is>
       </c>
       <c r="F14" s="24" t="n"/>
-      <c r="G14" s="77" t="n"/>
-      <c r="H14" s="78">
+      <c r="G14" s="75" t="n"/>
+      <c r="H14" s="76">
         <f>H5*15%</f>
         <v>1038690</v>
       </c>
-      <c r="I14" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="73">
+      <c r="I14" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="71">
         <f>IF(H14="","",H14+I14)</f>
         <v>1038690</v>
       </c>
@@ -3781,21 +3778,21 @@
       </c>
     </row>
     <row r="3" ht="27" customHeight="1" s="1">
-      <c r="D3" s="45" t="inlineStr">
+      <c r="D3" s="43" t="inlineStr">
         <is>
           <t>平均人日单价(元)</t>
         </is>
       </c>
-      <c r="E3" s="46">
+      <c r="E3" s="44">
         <f>IFERROR(SUM(F5:F14)/SUM(D5:D14),0)</f>
         <v>1392.43917152624</v>
       </c>
-      <c r="F3" s="47" t="inlineStr">
+      <c r="F3" s="45" t="inlineStr">
         <is>
           <t>自动计算：角色人工成本合计÷总计划人天，不手工填写</t>
         </is>
       </c>
-      <c r="G3" s="48" t="n"/>
+      <c r="G3" s="46" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1" s="1">
       <c r="A4" s="12" t="inlineStr">
@@ -3835,27 +3832,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="49" t="inlineStr">
+      <c r="A5" s="47" t="inlineStr">
         <is>
           <t>PGM</t>
         </is>
       </c>
-      <c r="B5" s="49" t="inlineStr">
+      <c r="B5" s="47" t="inlineStr">
         <is>
           <t>项目集经理</t>
         </is>
       </c>
-      <c r="C5" s="79" t="n">
+      <c r="C5" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="80">
+      <c r="D5" s="78">
         <f>月度投入明细!AP5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="52" t="n">
+      <c r="E5" s="50" t="n">
         <v>1900</v>
       </c>
-      <c r="F5" s="53">
+      <c r="F5" s="51">
         <f>D5*E5</f>
         <v>0</v>
       </c>
@@ -3866,27 +3863,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="49" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="B6" s="49" t="inlineStr">
+      <c r="B6" s="47" t="inlineStr">
         <is>
           <t>项目经理</t>
         </is>
       </c>
-      <c r="C6" s="79" t="n">
+      <c r="C6" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="80">
+      <c r="D6" s="78">
         <f>月度投入明细!AP6</f>
         <v>336</v>
       </c>
-      <c r="E6" s="52" t="n">
+      <c r="E6" s="50" t="n">
         <v>1700</v>
       </c>
-      <c r="F6" s="53">
+      <c r="F6" s="51">
         <f>D6*E6</f>
         <v>571200</v>
       </c>
@@ -3897,27 +3894,27 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="49" t="inlineStr">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>TM</t>
         </is>
       </c>
-      <c r="B7" s="49" t="inlineStr">
+      <c r="B7" s="47" t="inlineStr">
         <is>
           <t>技术经理</t>
         </is>
       </c>
-      <c r="C7" s="79" t="n">
+      <c r="C7" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="80">
+      <c r="D7" s="78">
         <f>月度投入明细!AP7</f>
         <v>577</v>
       </c>
-      <c r="E7" s="52" t="n">
+      <c r="E7" s="50" t="n">
         <v>1700</v>
       </c>
-      <c r="F7" s="53">
+      <c r="F7" s="51">
         <f>D7*E7</f>
         <v>980900</v>
       </c>
@@ -3928,27 +3925,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="49" t="inlineStr">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>PDM</t>
         </is>
       </c>
-      <c r="B8" s="49" t="inlineStr">
+      <c r="B8" s="47" t="inlineStr">
         <is>
           <t>产品经理</t>
         </is>
       </c>
-      <c r="C8" s="79" t="n">
+      <c r="C8" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="80">
+      <c r="D8" s="78">
         <f>月度投入明细!AP8</f>
         <v>493</v>
       </c>
-      <c r="E8" s="52" t="n">
+      <c r="E8" s="50" t="n">
         <v>1700</v>
       </c>
-      <c r="F8" s="53">
+      <c r="F8" s="51">
         <f>D8*E8</f>
         <v>838100</v>
       </c>
@@ -3959,27 +3956,27 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="49" t="inlineStr">
+      <c r="A9" s="47" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="B9" s="49" t="inlineStr">
+      <c r="B9" s="47" t="inlineStr">
         <is>
           <t>美工</t>
         </is>
       </c>
-      <c r="C9" s="79" t="n">
+      <c r="C9" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="80">
+      <c r="D9" s="78">
         <f>月度投入明细!AP9</f>
         <v>42</v>
       </c>
-      <c r="E9" s="52" t="n">
+      <c r="E9" s="50" t="n">
         <v>900</v>
       </c>
-      <c r="F9" s="53">
+      <c r="F9" s="51">
         <f>D9*E9</f>
         <v>37800</v>
       </c>
@@ -3990,27 +3987,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="49" t="inlineStr">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>SDEV</t>
         </is>
       </c>
-      <c r="B10" s="49" t="inlineStr">
+      <c r="B10" s="47" t="inlineStr">
         <is>
           <t>高级开发人员</t>
         </is>
       </c>
-      <c r="C10" s="79" t="n">
+      <c r="C10" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="80">
+      <c r="D10" s="78">
         <f>月度投入明细!AP10</f>
         <v>421</v>
       </c>
-      <c r="E10" s="52" t="n">
+      <c r="E10" s="50" t="n">
         <v>1500</v>
       </c>
-      <c r="F10" s="53">
+      <c r="F10" s="51">
         <f>D10*E10</f>
         <v>631500</v>
       </c>
@@ -4021,27 +4018,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="49" t="inlineStr">
+      <c r="A11" s="47" t="inlineStr">
         <is>
           <t>MDEV</t>
         </is>
       </c>
-      <c r="B11" s="49" t="inlineStr">
+      <c r="B11" s="47" t="inlineStr">
         <is>
           <t>中级开发人员</t>
         </is>
       </c>
-      <c r="C11" s="79" t="n">
+      <c r="C11" s="77" t="n">
         <v>14</v>
       </c>
-      <c r="D11" s="80">
+      <c r="D11" s="78">
         <f>月度投入明细!AP11</f>
         <v>2327</v>
       </c>
-      <c r="E11" s="52" t="n">
+      <c r="E11" s="50" t="n">
         <v>1300</v>
       </c>
-      <c r="F11" s="53">
+      <c r="F11" s="51">
         <f>D11*E11</f>
         <v>3025100</v>
       </c>
@@ -4052,27 +4049,27 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="49" t="inlineStr">
+      <c r="A12" s="47" t="inlineStr">
         <is>
           <t>SQA</t>
         </is>
       </c>
-      <c r="B12" s="49" t="inlineStr">
+      <c r="B12" s="47" t="inlineStr">
         <is>
           <t>高级测试人员</t>
         </is>
       </c>
-      <c r="C12" s="79" t="n">
+      <c r="C12" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="80">
+      <c r="D12" s="78">
         <f>月度投入明细!AP12</f>
         <v>210</v>
       </c>
-      <c r="E12" s="52" t="n">
+      <c r="E12" s="50" t="n">
         <v>1300</v>
       </c>
-      <c r="F12" s="53">
+      <c r="F12" s="51">
         <f>D12*E12</f>
         <v>273000</v>
       </c>
@@ -4083,27 +4080,27 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="49" t="inlineStr">
+      <c r="A13" s="47" t="inlineStr">
         <is>
           <t>MQA</t>
         </is>
       </c>
-      <c r="B13" s="49" t="inlineStr">
+      <c r="B13" s="47" t="inlineStr">
         <is>
           <t>中级测试人员</t>
         </is>
       </c>
-      <c r="C13" s="79" t="n">
+      <c r="C13" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="80">
+      <c r="D13" s="78">
         <f>月度投入明细!AP13</f>
         <v>357</v>
       </c>
-      <c r="E13" s="52" t="n">
+      <c r="E13" s="50" t="n">
         <v>1000</v>
       </c>
-      <c r="F13" s="53">
+      <c r="F13" s="51">
         <f>D13*E13</f>
         <v>357000</v>
       </c>
@@ -4114,27 +4111,27 @@
       </c>
     </row>
     <row r="14" ht="17.55" customHeight="1" s="1">
-      <c r="A14" s="49" t="inlineStr">
+      <c r="A14" s="47" t="inlineStr">
         <is>
           <t>CM</t>
         </is>
       </c>
-      <c r="B14" s="49" t="inlineStr">
+      <c r="B14" s="47" t="inlineStr">
         <is>
           <t>配置人员</t>
         </is>
       </c>
-      <c r="C14" s="79" t="n">
+      <c r="C14" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="80">
+      <c r="D14" s="78">
         <f>月度投入明细!AP14</f>
         <v>210</v>
       </c>
-      <c r="E14" s="52" t="n">
+      <c r="E14" s="50" t="n">
         <v>1000</v>
       </c>
-      <c r="F14" s="53">
+      <c r="F14" s="51">
         <f>D14*E14</f>
         <v>210000</v>
       </c>
@@ -4145,29 +4142,29 @@
       </c>
     </row>
     <row r="15" ht="17.55" customHeight="1" s="1">
-      <c r="A15" s="54" t="inlineStr">
+      <c r="A15" s="52" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B15" s="54" t="n"/>
-      <c r="C15" s="81">
+      <c r="B15" s="52" t="n"/>
+      <c r="C15" s="79">
         <f>SUM(C5:C14)</f>
         <v>27</v>
       </c>
-      <c r="D15" s="81">
+      <c r="D15" s="79">
         <f>SUM(D5:D14)</f>
         <v>4973</v>
       </c>
-      <c r="E15" s="56">
+      <c r="E15" s="54">
         <f>$E$3</f>
         <v>1392.43917152624</v>
       </c>
-      <c r="F15" s="56">
+      <c r="F15" s="54">
         <f>D15*E15</f>
         <v>6924600</v>
       </c>
-      <c r="G15" s="57" t="n"/>
+      <c r="G15" s="55" t="n"/>
     </row>
     <row r="16" ht="17.55" customHeight="1" s="1"/>
   </sheetData>
@@ -4185,54 +4182,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS16"/>
+  <dimension ref="A1:AT16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="16" customWidth="1" style="1" min="1" max="1"/>
-    <col width="10" customWidth="1" style="1" min="2" max="21"/>
-    <col width="10" customWidth="1" style="1" min="3" max="3"/>
-    <col width="10" customWidth="1" style="1" min="4" max="4"/>
-    <col width="10" customWidth="1" style="1" min="5" max="5"/>
-    <col width="10" customWidth="1" style="1" min="6" max="6"/>
-    <col width="10" customWidth="1" style="1" min="7" max="7"/>
-    <col width="10" customWidth="1" style="1" min="8" max="8"/>
-    <col width="10" customWidth="1" style="1" min="9" max="9"/>
-    <col width="10" customWidth="1" style="1" min="10" max="10"/>
-    <col width="10" customWidth="1" style="1" min="11" max="11"/>
-    <col width="10" customWidth="1" style="1" min="12" max="12"/>
-    <col width="10" customWidth="1" style="1" min="13" max="13"/>
-    <col width="10" customWidth="1" style="1" min="14" max="14"/>
-    <col width="10" customWidth="1" style="1" min="15" max="15"/>
-    <col width="10" customWidth="1" style="1" min="16" max="16"/>
-    <col width="10" customWidth="1" style="1" min="17" max="17"/>
-    <col width="10" customWidth="1" style="1" min="18" max="18"/>
-    <col width="10" customWidth="1" style="1" min="19" max="19"/>
-    <col width="10" customWidth="1" style="1" min="20" max="20"/>
-    <col width="10" customWidth="1" style="1" min="21" max="21"/>
-    <col width="10" customWidth="1" style="1" min="22" max="24"/>
-    <col width="10" customWidth="1" style="1" min="23" max="23"/>
-    <col width="10" customWidth="1" style="1" min="24" max="24"/>
-    <col width="10" customWidth="1" style="1" min="25" max="25"/>
-    <col width="10" customWidth="1" style="1" min="26" max="26"/>
-    <col width="10" customWidth="1" style="1" min="27" max="27"/>
-    <col width="10" customWidth="1" style="1" min="28" max="28"/>
-    <col width="10" customWidth="1" style="1" min="29" max="29"/>
-    <col width="10" customWidth="1" style="1" min="30" max="30"/>
-    <col width="10" customWidth="1" style="1" min="31" max="31"/>
-    <col width="10" customWidth="1" style="1" min="32" max="32"/>
-    <col width="10" customWidth="1" style="1" min="33" max="33"/>
-    <col width="10" customWidth="1" style="1" min="34" max="34"/>
-    <col width="10" customWidth="1" style="1" min="35" max="35"/>
-    <col width="10" customWidth="1" style="1" min="36" max="36"/>
-    <col width="10" customWidth="1" style="1" min="37" max="37"/>
-    <col width="10" customWidth="1" style="1" min="38" max="38"/>
-    <col width="10" customWidth="1" style="1" min="39" max="39"/>
-    <col width="10" customWidth="1" style="1" min="40" max="40"/>
-    <col width="10" customWidth="1" style="1" min="41" max="41"/>
-    <col width="12" customWidth="1" style="1" min="42" max="42"/>
-    <col width="12" customWidth="1" style="1" min="43" max="43"/>
-    <col width="12" customWidth="1" style="1" min="44" max="44"/>
-    <col width="12" customWidth="1" style="1" min="45" max="45"/>
+    <col width="10" customWidth="1" style="1" min="2" max="41"/>
+    <col width="12" customWidth="1" style="1" min="42" max="45"/>
+    <col width="12" customWidth="1" style="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4245,1597 +4201,2036 @@
     <row r="2" ht="40" customHeight="1" s="1">
       <c r="A2" s="35" t="inlineStr">
         <is>
-          <t>按角色×月份的计划/实际投入人天，由项目团队维护；计划列为人工成本预算计划人天的唯一来源（人工成本预算 D 列引用本表“计划合计”列，预算人天/差异列自动核对，差异为 0 即一致）；每月按实际排产更新实际列，修改后平均人日单价与人工成本自动重算。</t>
+          <t>按角色×月份的计划/实际投入人天，由项目团队维护；计划列为人工成本预算计划人天的唯一来源（人工成本预算 D 列引用本表“计划合计”列，预算人天列保持与人工成本预算核对）；差异列=计划合计−实际合计，反映投入进度偏差；完成率=实际合计/计划合计；每月按实际排产更新实际列，修改后平均人日单价与人工成本自动重算。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="37" t="inlineStr">
+      <c r="B3" s="36" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D3" s="37" t="inlineStr">
+      <c r="C3" s="70" t="n"/>
+      <c r="D3" s="36" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="F3" s="37" t="inlineStr">
+      <c r="E3" s="70" t="n"/>
+      <c r="F3" s="36" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="H3" s="37" t="inlineStr">
+      <c r="G3" s="70" t="n"/>
+      <c r="H3" s="36" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="J3" s="37" t="inlineStr">
+      <c r="I3" s="70" t="n"/>
+      <c r="J3" s="36" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="L3" s="37" t="inlineStr">
+      <c r="K3" s="70" t="n"/>
+      <c r="L3" s="36" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="N3" s="37" t="inlineStr">
+      <c r="M3" s="70" t="n"/>
+      <c r="N3" s="36" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="P3" s="37" t="inlineStr">
+      <c r="O3" s="70" t="n"/>
+      <c r="P3" s="36" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="R3" s="37" t="inlineStr">
+      <c r="Q3" s="70" t="n"/>
+      <c r="R3" s="36" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="T3" s="37" t="inlineStr">
+      <c r="S3" s="70" t="n"/>
+      <c r="T3" s="36" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="V3" s="37" t="inlineStr">
+      <c r="U3" s="70" t="n"/>
+      <c r="V3" s="36" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="X3" s="37" t="inlineStr">
+      <c r="W3" s="70" t="n"/>
+      <c r="X3" s="36" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="Z3" s="37" t="inlineStr">
+      <c r="Y3" s="70" t="n"/>
+      <c r="Z3" s="36" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="AB3" s="37" t="inlineStr">
+      <c r="AA3" s="70" t="n"/>
+      <c r="AB3" s="36" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="AD3" s="37" t="inlineStr">
+      <c r="AC3" s="70" t="n"/>
+      <c r="AD3" s="36" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="AF3" s="37" t="inlineStr">
+      <c r="AE3" s="70" t="n"/>
+      <c r="AF3" s="36" t="inlineStr">
         <is>
           <t>2027-04</t>
         </is>
       </c>
-      <c r="AH3" s="37" t="inlineStr">
+      <c r="AG3" s="70" t="n"/>
+      <c r="AH3" s="36" t="inlineStr">
         <is>
           <t>2027-05</t>
         </is>
       </c>
-      <c r="AJ3" s="37" t="inlineStr">
+      <c r="AI3" s="70" t="n"/>
+      <c r="AJ3" s="36" t="inlineStr">
         <is>
           <t>2027-06</t>
         </is>
       </c>
-      <c r="AL3" s="37" t="inlineStr">
+      <c r="AK3" s="70" t="n"/>
+      <c r="AL3" s="36" t="inlineStr">
         <is>
           <t>2027-07</t>
         </is>
       </c>
-      <c r="AN3" s="37" t="inlineStr">
+      <c r="AM3" s="70" t="n"/>
+      <c r="AN3" s="36" t="inlineStr">
         <is>
           <t>2027-08</t>
         </is>
       </c>
+      <c r="AO3" s="70" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>角色</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>计划</t>
         </is>
       </c>
-      <c r="C4" s="37" t="inlineStr">
+      <c r="C4" s="36" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="36" t="inlineStr">
         <is>
           <t>计划</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="36" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="F4" s="37" t="inlineStr">
+      <c r="F4" s="36" t="inlineStr">
         <is>
           <t>计划</t>
         </is>
       </c>
-      <c r="G4" s="37" t="inlineStr">
+      <c r="G4" s="36" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="H4" s="37" t="inlineStr">
+      <c r="H4" s="36" t="inlineStr">
         <is>
           <t>计划</t>
         </is>
       </c>
-      <c r="I4" s="37" t="inlineStr">
+      <c r="I4" s="36" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="J4" s="37" t="inlineStr">
+      <c r="J4" s="36" t="inlineStr">
         <is>
           <t>计划</t>
         </is>
       </c>
-      <c r="K4" s="37" t="inlineStr">
+      <c r="K4" s="36" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="L4" s="37" t="inlineStr">
+      <c r="L4" s="36" t="inlineStr">
         <is>
           <t>计划</t>
         </is>
       </c>
-      <c r="M4" s="37" t="inlineStr">
+      <c r="M4" s="36" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="N4" s="37" t="inlineStr">
+      <c r="N4" s="36" t="inlineStr">
         <is>
           <t>计划</t>
         </is>
       </c>
-      <c r="O4" s="37" t="inlineStr">
+      <c r="O4" s="36" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="P4" s="37" t="inlineStr">
+      <c r="P4" s="36" t="inlineStr">
         <is>
           <t>计划</t>
         </is>
       </c>
-      <c r="Q4" s="37" t="inlineStr">
+      <c r="Q4" s="36" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="R4" s="37" t="inlineStr">
+      <c r="R4" s="36" t="inlineStr">
         <is>
           <t>计划</t>
         </is>
       </c>
-      <c r="S4" s="37" t="inlineStr">
+      <c r="S4" s="36" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="T4" s="37" t="inlineStr">
+      <c r="T4" s="36" t="inlineStr">
         <is>
           <t>计划</t>
         </is>
       </c>
-      <c r="U4" s="37" t="inlineStr">
+      <c r="U4" s="36" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="V4" s="37" t="inlineStr">
+      <c r="V4" s="36" t="inlineStr">
         <is>
           <t>计划</t>
         </is>
       </c>
-      <c r="W4" s="37" t="inlineStr">
+      <c r="W4" s="36" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="X4" s="37" t="inlineStr">
+      <c r="X4" s="36" t="inlineStr">
         <is>
           <t>计划</t>
         </is>
       </c>
-      <c r="Y4" s="37" t="inlineStr">
+      <c r="Y4" s="36" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="Z4" s="37" t="inlineStr">
+      <c r="Z4" s="36" t="inlineStr">
         <is>
           <t>计划</t>
         </is>
       </c>
-      <c r="AA4" s="37" t="inlineStr">
+      <c r="AA4" s="36" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="AB4" s="37" t="inlineStr">
+      <c r="AB4" s="36" t="inlineStr">
         <is>
           <t>计划</t>
         </is>
       </c>
-      <c r="AC4" s="37" t="inlineStr">
+      <c r="AC4" s="36" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="AD4" s="37" t="inlineStr">
+      <c r="AD4" s="36" t="inlineStr">
         <is>
           <t>计划</t>
         </is>
       </c>
-      <c r="AE4" s="37" t="inlineStr">
+      <c r="AE4" s="36" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="AF4" s="37" t="inlineStr">
+      <c r="AF4" s="36" t="inlineStr">
         <is>
           <t>计划</t>
         </is>
       </c>
-      <c r="AG4" s="37" t="inlineStr">
+      <c r="AG4" s="36" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="AH4" s="37" t="inlineStr">
+      <c r="AH4" s="36" t="inlineStr">
         <is>
           <t>计划</t>
         </is>
       </c>
-      <c r="AI4" s="37" t="inlineStr">
+      <c r="AI4" s="36" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="AJ4" s="37" t="inlineStr">
+      <c r="AJ4" s="36" t="inlineStr">
         <is>
           <t>计划</t>
         </is>
       </c>
-      <c r="AK4" s="37" t="inlineStr">
+      <c r="AK4" s="36" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="AL4" s="37" t="inlineStr">
+      <c r="AL4" s="36" t="inlineStr">
         <is>
           <t>计划</t>
         </is>
       </c>
-      <c r="AM4" s="37" t="inlineStr">
+      <c r="AM4" s="36" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="AN4" s="37" t="inlineStr">
+      <c r="AN4" s="36" t="inlineStr">
         <is>
           <t>计划</t>
         </is>
       </c>
-      <c r="AO4" s="37" t="inlineStr">
+      <c r="AO4" s="36" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="AP4" s="37" t="inlineStr">
+      <c r="AP4" s="36" t="inlineStr">
         <is>
           <t>计划合计</t>
         </is>
       </c>
-      <c r="AQ4" s="37" t="inlineStr">
+      <c r="AQ4" s="36" t="inlineStr">
         <is>
           <t>实际合计</t>
         </is>
       </c>
-      <c r="AR4" s="37" t="inlineStr">
+      <c r="AR4" s="36" t="inlineStr">
         <is>
           <t>预算人天</t>
         </is>
       </c>
-      <c r="AS4" s="37" t="inlineStr">
-        <is>
-          <t>差异(计划-预算)</t>
+      <c r="AS4" s="36" t="inlineStr">
+        <is>
+          <t>差异(计划-实际)</t>
+        </is>
+      </c>
+      <c r="AT4" s="36" t="inlineStr">
+        <is>
+          <t>完成率(实际/计划)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>项目集经理</t>
         </is>
       </c>
-      <c r="B5" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="40" t="n"/>
-      <c r="D5" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="40" t="n"/>
-      <c r="F5" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="40" t="n"/>
-      <c r="H5" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="40" t="n"/>
-      <c r="J5" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="40" t="n"/>
-      <c r="L5" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="40" t="n"/>
-      <c r="N5" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="40" t="n"/>
-      <c r="P5" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="40" t="n"/>
-      <c r="R5" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="40" t="n"/>
-      <c r="T5" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="40" t="n"/>
-      <c r="V5" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="40" t="n"/>
-      <c r="X5" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="40" t="n"/>
-      <c r="Z5" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="40" t="n"/>
-      <c r="AB5" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="40" t="n"/>
-      <c r="AD5" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="40" t="n"/>
-      <c r="AF5" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="40" t="n"/>
-      <c r="AH5" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="40" t="n"/>
-      <c r="AJ5" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="40" t="n"/>
-      <c r="AL5" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" s="40" t="n"/>
-      <c r="AN5" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" s="40" t="n"/>
-      <c r="AP5" s="40">
+      <c r="B5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="39">
         <f>SUMIF($B$4:$AO$4,"计划",B5:AO5)</f>
         <v>0</v>
       </c>
-      <c r="AQ5" s="40">
+      <c r="AQ5" s="39">
         <f>SUMIF($B$4:$AO$4,"实际",B5:AO5)</f>
         <v>0</v>
       </c>
-      <c r="AR5" s="40">
+      <c r="AR5" s="39">
         <f>人工成本预算!D5</f>
         <v>0</v>
       </c>
-      <c r="AS5" s="40">
-        <f>AP5-AR5</f>
-        <v>0</v>
+      <c r="AS5" s="39">
+        <f>AP5-AQ5</f>
+        <v>0</v>
+      </c>
+      <c r="AT5" s="80">
+        <f>IF(AP5=0,"",AQ5/AP5)</f>
+        <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="A6" s="38" t="inlineStr">
         <is>
           <t>项目经理</t>
         </is>
       </c>
-      <c r="B6" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="40" t="n"/>
-      <c r="D6" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="40" t="n"/>
-      <c r="F6" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="40" t="n"/>
-      <c r="H6" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="40" t="n"/>
-      <c r="J6" s="40" t="n">
+      <c r="B6" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="K6" s="40" t="n"/>
-      <c r="L6" s="40" t="n">
+      <c r="K6" s="40" t="n">
         <v>21</v>
       </c>
-      <c r="M6" s="40" t="n"/>
-      <c r="N6" s="40" t="n">
+      <c r="L6" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="O6" s="40" t="n"/>
-      <c r="P6" s="40" t="n">
+      <c r="M6" s="40" t="n">
         <v>21</v>
       </c>
-      <c r="Q6" s="40" t="n"/>
-      <c r="R6" s="40" t="n">
+      <c r="N6" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="S6" s="40" t="n"/>
-      <c r="T6" s="40" t="n">
+      <c r="O6" s="40" t="n">
         <v>21</v>
       </c>
-      <c r="U6" s="40" t="n"/>
-      <c r="V6" s="40" t="n">
+      <c r="P6" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="W6" s="40" t="n"/>
-      <c r="X6" s="40" t="n">
+      <c r="Q6" s="40" t="n">
         <v>21</v>
       </c>
-      <c r="Y6" s="40" t="n"/>
-      <c r="Z6" s="40" t="n">
+      <c r="R6" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AA6" s="40" t="n"/>
-      <c r="AB6" s="40" t="n">
+      <c r="S6" s="40" t="n">
         <v>21</v>
       </c>
-      <c r="AC6" s="40" t="n"/>
-      <c r="AD6" s="40" t="n">
+      <c r="T6" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AE6" s="40" t="n"/>
-      <c r="AF6" s="40" t="n">
+      <c r="U6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AG6" s="40" t="n"/>
-      <c r="AH6" s="40" t="n">
+      <c r="W6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AI6" s="40" t="n"/>
-      <c r="AJ6" s="40" t="n">
+      <c r="Y6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AK6" s="40" t="n"/>
-      <c r="AL6" s="40" t="n">
+      <c r="AA6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AM6" s="40" t="n"/>
-      <c r="AN6" s="40" t="n">
+      <c r="AC6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AO6" s="40" t="n"/>
-      <c r="AP6" s="40">
+      <c r="AE6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="39" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="39" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="39" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="39" t="n">
+        <v>21</v>
+      </c>
+      <c r="AM6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="39" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="39">
         <f>SUMIF($B$4:$AO$4,"计划",B6:AO6)</f>
         <v>336</v>
       </c>
-      <c r="AQ6" s="40">
+      <c r="AQ6" s="39">
         <f>SUMIF($B$4:$AO$4,"实际",B6:AO6)</f>
-        <v>0</v>
-      </c>
-      <c r="AR6" s="40">
+        <v>105</v>
+      </c>
+      <c r="AR6" s="39">
         <f>人工成本预算!D6</f>
         <v>336</v>
       </c>
-      <c r="AS6" s="40">
-        <f>AP6-AR6</f>
-        <v>0</v>
+      <c r="AS6" s="39">
+        <f>AP6-AQ6</f>
+        <v>231</v>
+      </c>
+      <c r="AT6" s="80">
+        <f>IF(AP6=0,"",AQ6/AP6)</f>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="38" t="inlineStr">
         <is>
           <t>技术经理</t>
         </is>
       </c>
-      <c r="B7" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="40" t="n"/>
-      <c r="D7" s="40" t="n">
+      <c r="B7" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="E7" s="40" t="n"/>
-      <c r="F7" s="40" t="n">
+      <c r="E7" s="40" t="n">
         <v>21</v>
       </c>
-      <c r="G7" s="40" t="n"/>
-      <c r="H7" s="40" t="n">
+      <c r="F7" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="I7" s="40" t="n"/>
-      <c r="J7" s="40" t="n">
+      <c r="G7" s="40" t="n">
         <v>21</v>
       </c>
-      <c r="K7" s="40" t="n"/>
-      <c r="L7" s="40" t="n">
+      <c r="H7" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="M7" s="40" t="n"/>
-      <c r="N7" s="40" t="n">
+      <c r="I7" s="40" t="n">
         <v>21</v>
       </c>
-      <c r="O7" s="40" t="n"/>
-      <c r="P7" s="40" t="n">
+      <c r="J7" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="Q7" s="40" t="n"/>
-      <c r="R7" s="40" t="n">
+      <c r="K7" s="40" t="n">
         <v>21</v>
       </c>
-      <c r="S7" s="40" t="n"/>
-      <c r="T7" s="40" t="n">
+      <c r="L7" s="39" t="n">
+        <v>21</v>
+      </c>
+      <c r="M7" s="40" t="n">
+        <v>21</v>
+      </c>
+      <c r="N7" s="39" t="n">
+        <v>21</v>
+      </c>
+      <c r="O7" s="40" t="n">
+        <v>21</v>
+      </c>
+      <c r="P7" s="39" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q7" s="40" t="n">
+        <v>21</v>
+      </c>
+      <c r="R7" s="39" t="n">
+        <v>21</v>
+      </c>
+      <c r="S7" s="40" t="n">
+        <v>21</v>
+      </c>
+      <c r="T7" s="39" t="n">
         <v>31</v>
       </c>
-      <c r="U7" s="40" t="n"/>
-      <c r="V7" s="40" t="n">
+      <c r="U7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="W7" s="40" t="n"/>
-      <c r="X7" s="40" t="n">
+      <c r="W7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="Y7" s="40" t="n"/>
-      <c r="Z7" s="40" t="n">
+      <c r="Y7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AA7" s="40" t="n"/>
-      <c r="AB7" s="40" t="n">
+      <c r="AA7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AC7" s="40" t="n"/>
-      <c r="AD7" s="40" t="n">
+      <c r="AC7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AE7" s="40" t="n"/>
-      <c r="AF7" s="40" t="n">
+      <c r="AE7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AG7" s="40" t="n"/>
-      <c r="AH7" s="40" t="n">
+      <c r="AG7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AI7" s="40" t="n"/>
-      <c r="AJ7" s="40" t="n">
+      <c r="AI7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AK7" s="40" t="n"/>
-      <c r="AL7" s="40" t="n">
+      <c r="AK7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AM7" s="40" t="n"/>
-      <c r="AN7" s="40" t="n">
+      <c r="AM7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AO7" s="40" t="n"/>
-      <c r="AP7" s="40">
+      <c r="AO7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="39">
         <f>SUMIF($B$4:$AO$4,"计划",B7:AO7)</f>
         <v>577</v>
       </c>
-      <c r="AQ7" s="40">
+      <c r="AQ7" s="39">
         <f>SUMIF($B$4:$AO$4,"实际",B7:AO7)</f>
-        <v>0</v>
-      </c>
-      <c r="AR7" s="40">
+        <v>168</v>
+      </c>
+      <c r="AR7" s="39">
         <f>人工成本预算!D7</f>
         <v>577</v>
       </c>
-      <c r="AS7" s="40">
-        <f>AP7-AR7</f>
-        <v>0</v>
+      <c r="AS7" s="39">
+        <f>AP7-AQ7</f>
+        <v>409</v>
+      </c>
+      <c r="AT7" s="80">
+        <f>IF(AP7=0,"",AQ7/AP7)</f>
+        <v>0.291161178509532</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="39" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>产品经理</t>
         </is>
       </c>
-      <c r="B8" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="40" t="n"/>
-      <c r="D8" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="40" t="n"/>
-      <c r="F8" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="40" t="n"/>
-      <c r="H8" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="40" t="n"/>
-      <c r="J8" s="40" t="n">
+      <c r="B8" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="K8" s="40" t="n"/>
-      <c r="L8" s="40" t="n">
+      <c r="K8" s="40" t="n">
         <v>21</v>
       </c>
-      <c r="M8" s="40" t="n"/>
-      <c r="N8" s="40" t="n">
+      <c r="L8" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="O8" s="40" t="n"/>
-      <c r="P8" s="40" t="n">
+      <c r="M8" s="40" t="n">
         <v>21</v>
       </c>
-      <c r="Q8" s="40" t="n"/>
-      <c r="R8" s="40" t="n">
+      <c r="N8" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="S8" s="40" t="n"/>
-      <c r="T8" s="40" t="n">
+      <c r="O8" s="40" t="n">
+        <v>21</v>
+      </c>
+      <c r="P8" s="39" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q8" s="40" t="n">
+        <v>21</v>
+      </c>
+      <c r="R8" s="39" t="n">
+        <v>21</v>
+      </c>
+      <c r="S8" s="40" t="n">
+        <v>21</v>
+      </c>
+      <c r="T8" s="39" t="n">
         <v>31</v>
       </c>
-      <c r="U8" s="40" t="n"/>
-      <c r="V8" s="40" t="n">
+      <c r="U8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="W8" s="40" t="n"/>
-      <c r="X8" s="40" t="n">
+      <c r="W8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="Y8" s="40" t="n"/>
-      <c r="Z8" s="40" t="n">
+      <c r="Y8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AA8" s="40" t="n"/>
-      <c r="AB8" s="40" t="n">
+      <c r="AA8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AC8" s="40" t="n"/>
-      <c r="AD8" s="40" t="n">
+      <c r="AC8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AE8" s="40" t="n"/>
-      <c r="AF8" s="40" t="n">
+      <c r="AE8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AG8" s="40" t="n"/>
-      <c r="AH8" s="40" t="n">
+      <c r="AG8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AI8" s="40" t="n"/>
-      <c r="AJ8" s="40" t="n">
+      <c r="AI8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AK8" s="40" t="n"/>
-      <c r="AL8" s="40" t="n">
+      <c r="AK8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AM8" s="40" t="n"/>
-      <c r="AN8" s="40" t="n">
+      <c r="AM8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AO8" s="40" t="n"/>
-      <c r="AP8" s="40">
+      <c r="AO8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="39">
         <f>SUMIF($B$4:$AO$4,"计划",B8:AO8)</f>
         <v>493</v>
       </c>
-      <c r="AQ8" s="40">
+      <c r="AQ8" s="39">
         <f>SUMIF($B$4:$AO$4,"实际",B8:AO8)</f>
-        <v>0</v>
-      </c>
-      <c r="AR8" s="40">
+        <v>105</v>
+      </c>
+      <c r="AR8" s="39">
         <f>人工成本预算!D8</f>
         <v>493</v>
       </c>
-      <c r="AS8" s="40">
-        <f>AP8-AR8</f>
-        <v>0</v>
+      <c r="AS8" s="39">
+        <f>AP8-AQ8</f>
+        <v>388</v>
+      </c>
+      <c r="AT8" s="80">
+        <f>IF(AP8=0,"",AQ8/AP8)</f>
+        <v>0.212981744421907</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>美工</t>
         </is>
       </c>
-      <c r="B9" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="40" t="n"/>
-      <c r="D9" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="40" t="n"/>
-      <c r="F9" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="40" t="n"/>
-      <c r="H9" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="40" t="n"/>
-      <c r="J9" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="40" t="n"/>
-      <c r="L9" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="40" t="n"/>
-      <c r="N9" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="40" t="n"/>
-      <c r="P9" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="40" t="n"/>
-      <c r="R9" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="40" t="n"/>
-      <c r="T9" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="40" t="n"/>
-      <c r="V9" s="40" t="n">
+      <c r="B9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="W9" s="40" t="n"/>
-      <c r="X9" s="40" t="n">
+      <c r="W9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="Y9" s="40" t="n"/>
-      <c r="Z9" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="40" t="n"/>
-      <c r="AB9" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="40" t="n"/>
-      <c r="AD9" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="40" t="n"/>
-      <c r="AF9" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="40" t="n"/>
-      <c r="AH9" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="40" t="n"/>
-      <c r="AJ9" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="40" t="n"/>
-      <c r="AL9" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" s="40" t="n"/>
-      <c r="AN9" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" s="40" t="n"/>
-      <c r="AP9" s="40">
+      <c r="Y9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="39">
         <f>SUMIF($B$4:$AO$4,"计划",B9:AO9)</f>
         <v>42</v>
       </c>
-      <c r="AQ9" s="40">
+      <c r="AQ9" s="39">
         <f>SUMIF($B$4:$AO$4,"实际",B9:AO9)</f>
         <v>0</v>
       </c>
-      <c r="AR9" s="40">
+      <c r="AR9" s="39">
         <f>人工成本预算!D9</f>
         <v>42</v>
       </c>
-      <c r="AS9" s="40">
-        <f>AP9-AR9</f>
+      <c r="AS9" s="39">
+        <f>AP9-AQ9</f>
+        <v>42</v>
+      </c>
+      <c r="AT9" s="80">
+        <f>IF(AP9=0,"",AQ9/AP9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="39" t="inlineStr">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>高级开发人员</t>
         </is>
       </c>
-      <c r="B10" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="40" t="n"/>
-      <c r="D10" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="40" t="n"/>
-      <c r="F10" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="40" t="n"/>
-      <c r="H10" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="40" t="n"/>
-      <c r="J10" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="40" t="n"/>
-      <c r="L10" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="40" t="n"/>
-      <c r="N10" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="40" t="n"/>
-      <c r="P10" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="40" t="n"/>
-      <c r="R10" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="40" t="n"/>
-      <c r="T10" s="40" t="n">
+      <c r="B10" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="39" t="n">
         <v>22</v>
       </c>
-      <c r="U10" s="40" t="n"/>
-      <c r="V10" s="40" t="n">
+      <c r="U10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="W10" s="40" t="n"/>
-      <c r="X10" s="40" t="n">
+      <c r="W10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="Y10" s="40" t="n"/>
-      <c r="Z10" s="40" t="n">
+      <c r="Y10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AA10" s="40" t="n"/>
-      <c r="AB10" s="40" t="n">
+      <c r="AA10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AC10" s="40" t="n"/>
-      <c r="AD10" s="40" t="n">
+      <c r="AC10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AE10" s="40" t="n"/>
-      <c r="AF10" s="40" t="n">
+      <c r="AE10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AG10" s="40" t="n"/>
-      <c r="AH10" s="40" t="n">
+      <c r="AG10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AI10" s="40" t="n"/>
-      <c r="AJ10" s="40" t="n">
+      <c r="AI10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AK10" s="40" t="n"/>
-      <c r="AL10" s="40" t="n">
+      <c r="AK10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AM10" s="40" t="n"/>
-      <c r="AN10" s="40" t="n">
+      <c r="AM10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AO10" s="40" t="n"/>
-      <c r="AP10" s="40">
+      <c r="AO10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="39">
         <f>SUMIF($B$4:$AO$4,"计划",B10:AO10)</f>
         <v>421</v>
       </c>
-      <c r="AQ10" s="40">
+      <c r="AQ10" s="39">
         <f>SUMIF($B$4:$AO$4,"实际",B10:AO10)</f>
         <v>0</v>
       </c>
-      <c r="AR10" s="40">
+      <c r="AR10" s="39">
         <f>人工成本预算!D10</f>
         <v>421</v>
       </c>
-      <c r="AS10" s="40">
-        <f>AP10-AR10</f>
+      <c r="AS10" s="39">
+        <f>AP10-AQ10</f>
+        <v>421</v>
+      </c>
+      <c r="AT10" s="80">
+        <f>IF(AP10=0,"",AQ10/AP10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>中级开发人员</t>
         </is>
       </c>
-      <c r="B11" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="40" t="n"/>
-      <c r="D11" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="40" t="n"/>
-      <c r="F11" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="40" t="n"/>
-      <c r="H11" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="40" t="n"/>
-      <c r="J11" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="40" t="n"/>
-      <c r="L11" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="40" t="n"/>
-      <c r="N11" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="40" t="n"/>
-      <c r="P11" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="40" t="n"/>
-      <c r="R11" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="40" t="n"/>
-      <c r="T11" s="40" t="n">
+      <c r="B11" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="39" t="n">
         <v>80</v>
       </c>
-      <c r="U11" s="40" t="n"/>
-      <c r="V11" s="40" t="n">
+      <c r="U11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="39" t="n">
         <v>294</v>
       </c>
-      <c r="W11" s="40" t="n"/>
-      <c r="X11" s="40" t="n">
+      <c r="W11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="39" t="n">
         <v>294</v>
       </c>
-      <c r="Y11" s="40" t="n"/>
-      <c r="Z11" s="40" t="n">
+      <c r="Y11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="39" t="n">
         <v>294</v>
       </c>
-      <c r="AA11" s="40" t="n"/>
-      <c r="AB11" s="40" t="n">
+      <c r="AA11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="39" t="n">
         <v>294</v>
       </c>
-      <c r="AC11" s="40" t="n"/>
-      <c r="AD11" s="40" t="n">
+      <c r="AC11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="39" t="n">
         <v>294</v>
       </c>
-      <c r="AE11" s="40" t="n"/>
-      <c r="AF11" s="40" t="n">
+      <c r="AE11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="39" t="n">
         <v>294</v>
       </c>
-      <c r="AG11" s="40" t="n"/>
-      <c r="AH11" s="40" t="n">
+      <c r="AG11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="39" t="n">
         <v>210</v>
       </c>
-      <c r="AI11" s="40" t="n"/>
-      <c r="AJ11" s="40" t="n">
+      <c r="AI11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="39" t="n">
         <v>126</v>
       </c>
-      <c r="AK11" s="40" t="n"/>
-      <c r="AL11" s="40" t="n">
+      <c r="AK11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="39" t="n">
         <v>84</v>
       </c>
-      <c r="AM11" s="40" t="n"/>
-      <c r="AN11" s="40" t="n">
+      <c r="AM11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="39" t="n">
         <v>63</v>
       </c>
-      <c r="AO11" s="40" t="n"/>
-      <c r="AP11" s="40">
+      <c r="AO11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="39">
         <f>SUMIF($B$4:$AO$4,"计划",B11:AO11)</f>
         <v>2327</v>
       </c>
-      <c r="AQ11" s="40">
+      <c r="AQ11" s="39">
         <f>SUMIF($B$4:$AO$4,"实际",B11:AO11)</f>
         <v>0</v>
       </c>
-      <c r="AR11" s="40">
+      <c r="AR11" s="39">
         <f>人工成本预算!D11</f>
         <v>2327</v>
       </c>
-      <c r="AS11" s="40">
-        <f>AP11-AR11</f>
+      <c r="AS11" s="39">
+        <f>AP11-AQ11</f>
+        <v>2327</v>
+      </c>
+      <c r="AT11" s="80">
+        <f>IF(AP11=0,"",AQ11/AP11)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>高级测试人员</t>
         </is>
       </c>
-      <c r="B12" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="40" t="n"/>
-      <c r="D12" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="40" t="n"/>
-      <c r="F12" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="40" t="n"/>
-      <c r="H12" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="40" t="n"/>
-      <c r="J12" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="40" t="n"/>
-      <c r="L12" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="40" t="n"/>
-      <c r="N12" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="40" t="n"/>
-      <c r="P12" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="40" t="n"/>
-      <c r="R12" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="40" t="n"/>
-      <c r="T12" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="40" t="n"/>
-      <c r="V12" s="40" t="n">
+      <c r="B12" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="W12" s="40" t="n"/>
-      <c r="X12" s="40" t="n">
+      <c r="W12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="Y12" s="40" t="n"/>
-      <c r="Z12" s="40" t="n">
+      <c r="Y12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AA12" s="40" t="n"/>
-      <c r="AB12" s="40" t="n">
+      <c r="AA12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AC12" s="40" t="n"/>
-      <c r="AD12" s="40" t="n">
+      <c r="AC12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AE12" s="40" t="n"/>
-      <c r="AF12" s="40" t="n">
+      <c r="AE12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AG12" s="40" t="n"/>
-      <c r="AH12" s="40" t="n">
+      <c r="AG12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AI12" s="40" t="n"/>
-      <c r="AJ12" s="40" t="n">
+      <c r="AI12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AK12" s="40" t="n"/>
-      <c r="AL12" s="40" t="n">
+      <c r="AK12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AM12" s="40" t="n"/>
-      <c r="AN12" s="40" t="n">
+      <c r="AM12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AO12" s="40" t="n"/>
-      <c r="AP12" s="40">
+      <c r="AO12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="39">
         <f>SUMIF($B$4:$AO$4,"计划",B12:AO12)</f>
         <v>210</v>
       </c>
-      <c r="AQ12" s="40">
+      <c r="AQ12" s="39">
         <f>SUMIF($B$4:$AO$4,"实际",B12:AO12)</f>
         <v>0</v>
       </c>
-      <c r="AR12" s="40">
+      <c r="AR12" s="39">
         <f>人工成本预算!D12</f>
         <v>210</v>
       </c>
-      <c r="AS12" s="40">
-        <f>AP12-AR12</f>
+      <c r="AS12" s="39">
+        <f>AP12-AQ12</f>
+        <v>210</v>
+      </c>
+      <c r="AT12" s="80">
+        <f>IF(AP12=0,"",AQ12/AP12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="39" t="inlineStr">
+      <c r="A13" s="38" t="inlineStr">
         <is>
           <t>中级测试人员</t>
         </is>
       </c>
-      <c r="B13" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="40" t="n"/>
-      <c r="D13" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="40" t="n"/>
-      <c r="F13" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="40" t="n"/>
-      <c r="H13" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="40" t="n"/>
-      <c r="J13" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="40" t="n"/>
-      <c r="L13" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="40" t="n"/>
-      <c r="N13" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="40" t="n"/>
-      <c r="P13" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="40" t="n"/>
-      <c r="R13" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="40" t="n"/>
-      <c r="T13" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="40" t="n"/>
-      <c r="V13" s="40" t="n">
+      <c r="B13" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="W13" s="40" t="n"/>
-      <c r="X13" s="40" t="n">
+      <c r="W13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="Y13" s="40" t="n"/>
-      <c r="Z13" s="40" t="n">
+      <c r="Y13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AA13" s="40" t="n"/>
-      <c r="AB13" s="40" t="n">
+      <c r="AA13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AC13" s="40" t="n"/>
-      <c r="AD13" s="40" t="n">
+      <c r="AC13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AE13" s="40" t="n"/>
-      <c r="AF13" s="40" t="n">
+      <c r="AE13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AG13" s="40" t="n"/>
-      <c r="AH13" s="40" t="n">
+      <c r="AG13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="39" t="n">
         <v>42</v>
       </c>
-      <c r="AI13" s="40" t="n"/>
-      <c r="AJ13" s="40" t="n">
+      <c r="AI13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AK13" s="40" t="n"/>
-      <c r="AL13" s="40" t="n">
+      <c r="AK13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AM13" s="40" t="n"/>
-      <c r="AN13" s="40" t="n">
+      <c r="AM13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AO13" s="40" t="n"/>
-      <c r="AP13" s="40">
+      <c r="AO13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="39">
         <f>SUMIF($B$4:$AO$4,"计划",B13:AO13)</f>
         <v>357</v>
       </c>
-      <c r="AQ13" s="40">
+      <c r="AQ13" s="39">
         <f>SUMIF($B$4:$AO$4,"实际",B13:AO13)</f>
         <v>0</v>
       </c>
-      <c r="AR13" s="40">
+      <c r="AR13" s="39">
         <f>人工成本预算!D13</f>
         <v>357</v>
       </c>
-      <c r="AS13" s="40">
-        <f>AP13-AR13</f>
+      <c r="AS13" s="39">
+        <f>AP13-AQ13</f>
+        <v>357</v>
+      </c>
+      <c r="AT13" s="80">
+        <f>IF(AP13=0,"",AQ13/AP13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="17.55" customHeight="1" s="1">
-      <c r="A14" s="39" t="inlineStr">
+      <c r="A14" s="38" t="inlineStr">
         <is>
           <t>配置人员</t>
         </is>
       </c>
-      <c r="B14" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="40" t="n"/>
-      <c r="D14" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="40" t="n"/>
-      <c r="F14" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="40" t="n"/>
-      <c r="H14" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="40" t="n"/>
-      <c r="J14" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="40" t="n"/>
-      <c r="L14" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="40" t="n"/>
-      <c r="N14" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="40" t="n"/>
-      <c r="P14" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="40" t="n"/>
-      <c r="R14" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="40" t="n"/>
-      <c r="T14" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="40" t="n"/>
-      <c r="V14" s="40" t="n">
+      <c r="B14" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="W14" s="40" t="n"/>
-      <c r="X14" s="40" t="n">
+      <c r="W14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="Y14" s="40" t="n"/>
-      <c r="Z14" s="40" t="n">
+      <c r="Y14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AA14" s="40" t="n"/>
-      <c r="AB14" s="40" t="n">
+      <c r="AA14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AC14" s="40" t="n"/>
-      <c r="AD14" s="40" t="n">
+      <c r="AC14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AE14" s="40" t="n"/>
-      <c r="AF14" s="40" t="n">
+      <c r="AE14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AG14" s="40" t="n"/>
-      <c r="AH14" s="40" t="n">
+      <c r="AG14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AI14" s="40" t="n"/>
-      <c r="AJ14" s="40" t="n">
+      <c r="AI14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AK14" s="40" t="n"/>
-      <c r="AL14" s="40" t="n">
+      <c r="AK14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AM14" s="40" t="n"/>
-      <c r="AN14" s="40" t="n">
+      <c r="AM14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="AO14" s="40" t="n"/>
-      <c r="AP14" s="40">
+      <c r="AO14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="39">
         <f>SUMIF($B$4:$AO$4,"计划",B14:AO14)</f>
         <v>210</v>
       </c>
-      <c r="AQ14" s="40">
+      <c r="AQ14" s="39">
         <f>SUMIF($B$4:$AO$4,"实际",B14:AO14)</f>
         <v>0</v>
       </c>
-      <c r="AR14" s="40">
+      <c r="AR14" s="39">
         <f>人工成本预算!D14</f>
         <v>210</v>
       </c>
-      <c r="AS14" s="40">
-        <f>AP14-AR14</f>
+      <c r="AS14" s="39">
+        <f>AP14-AQ14</f>
+        <v>210</v>
+      </c>
+      <c r="AT14" s="80">
+        <f>IF(AP14=0,"",AQ14/AP14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="17.55" customHeight="1" s="1">
-      <c r="A15" s="42" t="inlineStr">
+      <c r="A15" s="41" t="inlineStr">
         <is>
           <t>合计人天</t>
         </is>
       </c>
-      <c r="B15" s="40">
+      <c r="B15" s="39">
         <f>SUM(B5:B14)</f>
         <v>0</v>
       </c>
-      <c r="C15" s="40">
+      <c r="C15" s="39">
         <f>SUM(C5:C14)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="40">
+      <c r="D15" s="39">
         <f>SUM(D5:D14)</f>
         <v>21</v>
       </c>
-      <c r="E15" s="40">
+      <c r="E15" s="39">
         <f>SUM(E5:E14)</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="40">
+        <v>21</v>
+      </c>
+      <c r="F15" s="39">
         <f>SUM(F5:F14)</f>
         <v>21</v>
       </c>
-      <c r="G15" s="40">
+      <c r="G15" s="39">
         <f>SUM(G5:G14)</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="40">
+        <v>21</v>
+      </c>
+      <c r="H15" s="39">
         <f>SUM(H5:H14)</f>
         <v>21</v>
       </c>
-      <c r="I15" s="40">
+      <c r="I15" s="39">
         <f>SUM(I5:I14)</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="40">
+        <v>21</v>
+      </c>
+      <c r="J15" s="39">
         <f>SUM(J5:J14)</f>
         <v>63</v>
       </c>
-      <c r="K15" s="40">
+      <c r="K15" s="39">
         <f>SUM(K5:K14)</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="40">
+        <v>63</v>
+      </c>
+      <c r="L15" s="39">
         <f>SUM(L5:L14)</f>
         <v>63</v>
       </c>
-      <c r="M15" s="40">
+      <c r="M15" s="39">
         <f>SUM(M5:M14)</f>
-        <v>0</v>
-      </c>
-      <c r="N15" s="40">
+        <v>63</v>
+      </c>
+      <c r="N15" s="39">
         <f>SUM(N5:N14)</f>
         <v>63</v>
       </c>
-      <c r="O15" s="40">
+      <c r="O15" s="39">
         <f>SUM(O5:O14)</f>
-        <v>0</v>
-      </c>
-      <c r="P15" s="40">
+        <v>63</v>
+      </c>
+      <c r="P15" s="39">
         <f>SUM(P5:P14)</f>
         <v>63</v>
       </c>
-      <c r="Q15" s="40">
+      <c r="Q15" s="39">
         <f>SUM(Q5:Q14)</f>
-        <v>0</v>
-      </c>
-      <c r="R15" s="40">
+        <v>63</v>
+      </c>
+      <c r="R15" s="39">
         <f>SUM(R5:R14)</f>
         <v>63</v>
       </c>
-      <c r="S15" s="40">
+      <c r="S15" s="39">
         <f>SUM(S5:S14)</f>
-        <v>0</v>
-      </c>
-      <c r="T15" s="40">
+        <v>63</v>
+      </c>
+      <c r="T15" s="39">
         <f>SUM(T5:T14)</f>
         <v>185</v>
       </c>
-      <c r="U15" s="40">
+      <c r="U15" s="39">
         <f>SUM(U5:U14)</f>
         <v>0</v>
       </c>
-      <c r="V15" s="40">
+      <c r="V15" s="39">
         <f>SUM(V5:V14)</f>
         <v>546</v>
       </c>
-      <c r="W15" s="40">
+      <c r="W15" s="39">
         <f>SUM(W5:W14)</f>
         <v>0</v>
       </c>
-      <c r="X15" s="40">
+      <c r="X15" s="39">
         <f>SUM(X5:X14)</f>
         <v>546</v>
       </c>
-      <c r="Y15" s="40">
+      <c r="Y15" s="39">
         <f>SUM(Y5:Y14)</f>
         <v>0</v>
       </c>
-      <c r="Z15" s="40">
+      <c r="Z15" s="39">
         <f>SUM(Z5:Z14)</f>
         <v>525</v>
       </c>
-      <c r="AA15" s="40">
+      <c r="AA15" s="39">
         <f>SUM(AA5:AA14)</f>
         <v>0</v>
       </c>
-      <c r="AB15" s="40">
+      <c r="AB15" s="39">
         <f>SUM(AB5:AB14)</f>
         <v>525</v>
       </c>
-      <c r="AC15" s="40">
+      <c r="AC15" s="39">
         <f>SUM(AC5:AC14)</f>
         <v>0</v>
       </c>
-      <c r="AD15" s="40">
+      <c r="AD15" s="39">
         <f>SUM(AD5:AD14)</f>
         <v>525</v>
       </c>
-      <c r="AE15" s="40">
+      <c r="AE15" s="39">
         <f>SUM(AE5:AE14)</f>
         <v>0</v>
       </c>
-      <c r="AF15" s="40">
+      <c r="AF15" s="39">
         <f>SUM(AF5:AF14)</f>
         <v>525</v>
       </c>
-      <c r="AG15" s="40">
+      <c r="AG15" s="39">
         <f>SUM(AG5:AG14)</f>
         <v>0</v>
       </c>
-      <c r="AH15" s="40">
+      <c r="AH15" s="39">
         <f>SUM(AH5:AH14)</f>
         <v>441</v>
       </c>
-      <c r="AI15" s="40">
+      <c r="AI15" s="39">
         <f>SUM(AI5:AI14)</f>
         <v>0</v>
       </c>
-      <c r="AJ15" s="40">
+      <c r="AJ15" s="39">
         <f>SUM(AJ5:AJ14)</f>
         <v>315</v>
       </c>
-      <c r="AK15" s="40">
+      <c r="AK15" s="39">
         <f>SUM(AK5:AK14)</f>
         <v>0</v>
       </c>
-      <c r="AL15" s="40">
+      <c r="AL15" s="39">
         <f>SUM(AL5:AL14)</f>
         <v>252</v>
       </c>
-      <c r="AM15" s="40">
+      <c r="AM15" s="39">
         <f>SUM(AM5:AM14)</f>
         <v>0</v>
       </c>
-      <c r="AN15" s="40">
+      <c r="AN15" s="39">
         <f>SUM(AN5:AN14)</f>
         <v>210</v>
       </c>
-      <c r="AO15" s="40">
+      <c r="AO15" s="39">
         <f>SUM(AO5:AO14)</f>
         <v>0</v>
       </c>
-      <c r="AP15" s="40">
+      <c r="AP15" s="39">
         <f>SUM(AP5:AP14)</f>
         <v>4973</v>
       </c>
-      <c r="AQ15" s="40">
+      <c r="AQ15" s="39">
         <f>SUM(AQ5:AQ14)</f>
-        <v>0</v>
-      </c>
-      <c r="AR15" s="40">
+        <v>378</v>
+      </c>
+      <c r="AR15" s="39">
         <f>SUM(AR5:AR14)</f>
         <v>4973</v>
       </c>
-      <c r="AS15" s="40">
-        <f>SUM(AS5:AS14)</f>
-        <v>0</v>
+      <c r="AS15" s="39">
+        <f>AP15-AQ15</f>
+        <v>4595</v>
+      </c>
+      <c r="AT15" s="80">
+        <f>IF(AP15=0,"",AQ15/AP15)</f>
+        <v>0.0760104564649105</v>
       </c>
     </row>
     <row r="16" ht="17.55" customHeight="1" s="1">
-      <c r="K16" s="44" t="n">
+      <c r="K16" s="42" t="n">
         <v>15</v>
       </c>
-      <c r="L16" s="44">
-        <f>L15/21</f>
-        <v>3</v>
-      </c>
-      <c r="M16" s="44">
-        <f>M15/21</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="44">
-        <f>N15/21</f>
-        <v>3</v>
-      </c>
-      <c r="O16" s="44">
-        <f>O15/21</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="44">
-        <f>P15/21</f>
-        <v>3</v>
-      </c>
-      <c r="Q16" s="44">
-        <f>Q15/21</f>
-        <v>0</v>
-      </c>
-      <c r="R16" s="44">
-        <f>R15/21</f>
-        <v>3</v>
-      </c>
-      <c r="S16" s="44">
-        <f>S15/21</f>
-        <v>0</v>
-      </c>
-      <c r="T16" s="44">
-        <f>T15/21</f>
-        <v>8.80952380952381</v>
-      </c>
-      <c r="U16" s="44">
-        <f>U15/21</f>
-        <v>0</v>
-      </c>
-      <c r="V16" s="44" t="n"/>
+      <c r="L16" s="42" t="n"/>
+      <c r="M16" s="42" t="n"/>
+      <c r="N16" s="42" t="n"/>
+      <c r="O16" s="42" t="n"/>
+      <c r="P16" s="42" t="n"/>
+      <c r="Q16" s="42" t="n"/>
+      <c r="R16" s="42" t="n"/>
+      <c r="S16" s="42" t="n"/>
+      <c r="T16" s="42" t="n"/>
+      <c r="U16" s="42" t="n"/>
+      <c r="V16" s="42" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -5985,13 +6380,13 @@
           <t>技术经理</t>
         </is>
       </c>
-      <c r="F5" s="74" t="n">
+      <c r="F5" s="72" t="n">
         <v>46290</v>
       </c>
-      <c r="G5" s="74" t="n">
+      <c r="G5" s="72" t="n">
         <v>46310</v>
       </c>
-      <c r="H5" s="82" t="n"/>
+      <c r="H5" s="81" t="n"/>
       <c r="I5" s="24" t="inlineStr">
         <is>
           <t>待估算</t>
@@ -6029,13 +6424,13 @@
           <t>技术经理</t>
         </is>
       </c>
-      <c r="F6" s="74" t="n">
+      <c r="F6" s="72" t="n">
         <v>46290</v>
       </c>
-      <c r="G6" s="74" t="n">
+      <c r="G6" s="72" t="n">
         <v>46310</v>
       </c>
-      <c r="H6" s="82" t="n"/>
+      <c r="H6" s="81" t="n"/>
       <c r="I6" s="24" t="inlineStr">
         <is>
           <t>待估算</t>
@@ -6073,13 +6468,13 @@
           <t>技术经理</t>
         </is>
       </c>
-      <c r="F7" s="74" t="n">
+      <c r="F7" s="72" t="n">
         <v>46290</v>
       </c>
-      <c r="G7" s="74" t="n">
+      <c r="G7" s="72" t="n">
         <v>46310</v>
       </c>
-      <c r="H7" s="82" t="n"/>
+      <c r="H7" s="81" t="n"/>
       <c r="I7" s="24" t="inlineStr">
         <is>
           <t>待估算</t>
@@ -6117,13 +6512,13 @@
           <t>配置人员</t>
         </is>
       </c>
-      <c r="F8" s="74" t="n">
+      <c r="F8" s="72" t="n">
         <v>46295</v>
       </c>
-      <c r="G8" s="74" t="n">
+      <c r="G8" s="72" t="n">
         <v>46311</v>
       </c>
-      <c r="H8" s="82" t="n"/>
+      <c r="H8" s="81" t="n"/>
       <c r="I8" s="24" t="inlineStr">
         <is>
           <t>待估算</t>
@@ -6161,13 +6556,13 @@
           <t>高级测试人员</t>
         </is>
       </c>
-      <c r="F9" s="74" t="n">
+      <c r="F9" s="72" t="n">
         <v>46387</v>
       </c>
-      <c r="G9" s="74" t="n">
+      <c r="G9" s="72" t="n">
         <v>46418</v>
       </c>
-      <c r="H9" s="82" t="n"/>
+      <c r="H9" s="81" t="n"/>
       <c r="I9" s="24" t="inlineStr">
         <is>
           <t>待估算</t>
@@ -6205,13 +6600,13 @@
           <t>产品经理</t>
         </is>
       </c>
-      <c r="F10" s="74" t="n">
+      <c r="F10" s="72" t="n">
         <v>46356</v>
       </c>
-      <c r="G10" s="74" t="n">
+      <c r="G10" s="72" t="n">
         <v>46387</v>
       </c>
-      <c r="H10" s="82" t="n"/>
+      <c r="H10" s="81" t="n"/>
       <c r="I10" s="24" t="inlineStr">
         <is>
           <t>待估算</t>
@@ -6249,13 +6644,13 @@
           <t>项目经理</t>
         </is>
       </c>
-      <c r="F11" s="74" t="n">
+      <c r="F11" s="72" t="n">
         <v>46311</v>
       </c>
-      <c r="G11" s="74" t="n">
+      <c r="G11" s="72" t="n">
         <v>46326</v>
       </c>
-      <c r="H11" s="82" t="n"/>
+      <c r="H11" s="81" t="n"/>
       <c r="I11" s="24" t="inlineStr">
         <is>
           <t>待估算</t>
@@ -6421,18 +6816,18 @@
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="24" t="n"/>
       <c r="E5" s="24" t="n"/>
-      <c r="F5" s="83" t="n"/>
-      <c r="G5" s="83" t="n"/>
-      <c r="H5" s="83" t="n"/>
-      <c r="I5" s="82" t="n"/>
-      <c r="J5" s="82" t="n"/>
-      <c r="K5" s="84">
+      <c r="F5" s="82" t="n"/>
+      <c r="G5" s="82" t="n"/>
+      <c r="H5" s="82" t="n"/>
+      <c r="I5" s="81" t="n"/>
+      <c r="J5" s="81" t="n"/>
+      <c r="K5" s="83">
         <f>IF(I5="","",I5+J5)</f>
         <v/>
       </c>
-      <c r="L5" s="82" t="n"/>
-      <c r="M5" s="82" t="n"/>
-      <c r="N5" s="84">
+      <c r="L5" s="81" t="n"/>
+      <c r="M5" s="81" t="n"/>
+      <c r="N5" s="83">
         <f>IF(K5="","",K5-M5)</f>
         <v/>
       </c>
@@ -6447,18 +6842,18 @@
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="24" t="n"/>
       <c r="E6" s="24" t="n"/>
-      <c r="F6" s="83" t="n"/>
-      <c r="G6" s="83" t="n"/>
-      <c r="H6" s="83" t="n"/>
-      <c r="I6" s="82" t="n"/>
-      <c r="J6" s="82" t="n"/>
-      <c r="K6" s="84">
+      <c r="F6" s="82" t="n"/>
+      <c r="G6" s="82" t="n"/>
+      <c r="H6" s="82" t="n"/>
+      <c r="I6" s="81" t="n"/>
+      <c r="J6" s="81" t="n"/>
+      <c r="K6" s="83">
         <f>IF(I6="","",I6+J6)</f>
         <v/>
       </c>
-      <c r="L6" s="82" t="n"/>
-      <c r="M6" s="82" t="n"/>
-      <c r="N6" s="84">
+      <c r="L6" s="81" t="n"/>
+      <c r="M6" s="81" t="n"/>
+      <c r="N6" s="83">
         <f>IF(K6="","",K6-M6)</f>
         <v/>
       </c>
@@ -6473,18 +6868,18 @@
       <c r="C7" s="24" t="n"/>
       <c r="D7" s="24" t="n"/>
       <c r="E7" s="24" t="n"/>
-      <c r="F7" s="83" t="n"/>
-      <c r="G7" s="83" t="n"/>
-      <c r="H7" s="83" t="n"/>
-      <c r="I7" s="82" t="n"/>
-      <c r="J7" s="82" t="n"/>
-      <c r="K7" s="84">
+      <c r="F7" s="82" t="n"/>
+      <c r="G7" s="82" t="n"/>
+      <c r="H7" s="82" t="n"/>
+      <c r="I7" s="81" t="n"/>
+      <c r="J7" s="81" t="n"/>
+      <c r="K7" s="83">
         <f>IF(I7="","",I7+J7)</f>
         <v/>
       </c>
-      <c r="L7" s="82" t="n"/>
-      <c r="M7" s="82" t="n"/>
-      <c r="N7" s="84">
+      <c r="L7" s="81" t="n"/>
+      <c r="M7" s="81" t="n"/>
+      <c r="N7" s="83">
         <f>IF(K7="","",K7-M7)</f>
         <v/>
       </c>
@@ -6499,18 +6894,18 @@
       <c r="C8" s="24" t="n"/>
       <c r="D8" s="24" t="n"/>
       <c r="E8" s="24" t="n"/>
-      <c r="F8" s="83" t="n"/>
-      <c r="G8" s="83" t="n"/>
-      <c r="H8" s="83" t="n"/>
-      <c r="I8" s="82" t="n"/>
-      <c r="J8" s="82" t="n"/>
-      <c r="K8" s="84">
+      <c r="F8" s="82" t="n"/>
+      <c r="G8" s="82" t="n"/>
+      <c r="H8" s="82" t="n"/>
+      <c r="I8" s="81" t="n"/>
+      <c r="J8" s="81" t="n"/>
+      <c r="K8" s="83">
         <f>IF(I8="","",I8+J8)</f>
         <v/>
       </c>
-      <c r="L8" s="82" t="n"/>
-      <c r="M8" s="82" t="n"/>
-      <c r="N8" s="84">
+      <c r="L8" s="81" t="n"/>
+      <c r="M8" s="81" t="n"/>
+      <c r="N8" s="83">
         <f>IF(K8="","",K8-M8)</f>
         <v/>
       </c>
@@ -6525,18 +6920,18 @@
       <c r="C9" s="24" t="n"/>
       <c r="D9" s="24" t="n"/>
       <c r="E9" s="24" t="n"/>
-      <c r="F9" s="83" t="n"/>
-      <c r="G9" s="83" t="n"/>
-      <c r="H9" s="83" t="n"/>
-      <c r="I9" s="82" t="n"/>
-      <c r="J9" s="82" t="n"/>
-      <c r="K9" s="84">
+      <c r="F9" s="82" t="n"/>
+      <c r="G9" s="82" t="n"/>
+      <c r="H9" s="82" t="n"/>
+      <c r="I9" s="81" t="n"/>
+      <c r="J9" s="81" t="n"/>
+      <c r="K9" s="83">
         <f>IF(I9="","",I9+J9)</f>
         <v/>
       </c>
-      <c r="L9" s="82" t="n"/>
-      <c r="M9" s="82" t="n"/>
-      <c r="N9" s="84">
+      <c r="L9" s="81" t="n"/>
+      <c r="M9" s="81" t="n"/>
+      <c r="N9" s="83">
         <f>IF(K9="","",K9-M9)</f>
         <v/>
       </c>
@@ -6551,18 +6946,18 @@
       <c r="C10" s="24" t="n"/>
       <c r="D10" s="24" t="n"/>
       <c r="E10" s="24" t="n"/>
-      <c r="F10" s="83" t="n"/>
-      <c r="G10" s="83" t="n"/>
-      <c r="H10" s="83" t="n"/>
-      <c r="I10" s="82" t="n"/>
-      <c r="J10" s="82" t="n"/>
-      <c r="K10" s="84">
+      <c r="F10" s="82" t="n"/>
+      <c r="G10" s="82" t="n"/>
+      <c r="H10" s="82" t="n"/>
+      <c r="I10" s="81" t="n"/>
+      <c r="J10" s="81" t="n"/>
+      <c r="K10" s="83">
         <f>IF(I10="","",I10+J10)</f>
         <v/>
       </c>
-      <c r="L10" s="82" t="n"/>
-      <c r="M10" s="82" t="n"/>
-      <c r="N10" s="84">
+      <c r="L10" s="81" t="n"/>
+      <c r="M10" s="81" t="n"/>
+      <c r="N10" s="83">
         <f>IF(K10="","",K10-M10)</f>
         <v/>
       </c>
@@ -6577,18 +6972,18 @@
       <c r="C11" s="24" t="n"/>
       <c r="D11" s="24" t="n"/>
       <c r="E11" s="24" t="n"/>
-      <c r="F11" s="83" t="n"/>
-      <c r="G11" s="83" t="n"/>
-      <c r="H11" s="83" t="n"/>
-      <c r="I11" s="82" t="n"/>
-      <c r="J11" s="82" t="n"/>
-      <c r="K11" s="84">
+      <c r="F11" s="82" t="n"/>
+      <c r="G11" s="82" t="n"/>
+      <c r="H11" s="82" t="n"/>
+      <c r="I11" s="81" t="n"/>
+      <c r="J11" s="81" t="n"/>
+      <c r="K11" s="83">
         <f>IF(I11="","",I11+J11)</f>
         <v/>
       </c>
-      <c r="L11" s="82" t="n"/>
-      <c r="M11" s="82" t="n"/>
-      <c r="N11" s="84">
+      <c r="L11" s="81" t="n"/>
+      <c r="M11" s="81" t="n"/>
+      <c r="N11" s="83">
         <f>IF(K11="","",K11-M11)</f>
         <v/>
       </c>
@@ -6603,18 +6998,18 @@
       <c r="C12" s="24" t="n"/>
       <c r="D12" s="24" t="n"/>
       <c r="E12" s="24" t="n"/>
-      <c r="F12" s="83" t="n"/>
-      <c r="G12" s="83" t="n"/>
-      <c r="H12" s="83" t="n"/>
-      <c r="I12" s="82" t="n"/>
-      <c r="J12" s="82" t="n"/>
-      <c r="K12" s="84">
+      <c r="F12" s="82" t="n"/>
+      <c r="G12" s="82" t="n"/>
+      <c r="H12" s="82" t="n"/>
+      <c r="I12" s="81" t="n"/>
+      <c r="J12" s="81" t="n"/>
+      <c r="K12" s="83">
         <f>IF(I12="","",I12+J12)</f>
         <v/>
       </c>
-      <c r="L12" s="82" t="n"/>
-      <c r="M12" s="82" t="n"/>
-      <c r="N12" s="84">
+      <c r="L12" s="81" t="n"/>
+      <c r="M12" s="81" t="n"/>
+      <c r="N12" s="83">
         <f>IF(K12="","",K12-M12)</f>
         <v/>
       </c>
@@ -6629,18 +7024,18 @@
       <c r="C13" s="24" t="n"/>
       <c r="D13" s="24" t="n"/>
       <c r="E13" s="24" t="n"/>
-      <c r="F13" s="83" t="n"/>
-      <c r="G13" s="83" t="n"/>
-      <c r="H13" s="83" t="n"/>
-      <c r="I13" s="82" t="n"/>
-      <c r="J13" s="82" t="n"/>
-      <c r="K13" s="84">
+      <c r="F13" s="82" t="n"/>
+      <c r="G13" s="82" t="n"/>
+      <c r="H13" s="82" t="n"/>
+      <c r="I13" s="81" t="n"/>
+      <c r="J13" s="81" t="n"/>
+      <c r="K13" s="83">
         <f>IF(I13="","",I13+J13)</f>
         <v/>
       </c>
-      <c r="L13" s="82" t="n"/>
-      <c r="M13" s="82" t="n"/>
-      <c r="N13" s="84">
+      <c r="L13" s="81" t="n"/>
+      <c r="M13" s="81" t="n"/>
+      <c r="N13" s="83">
         <f>IF(K13="","",K13-M13)</f>
         <v/>
       </c>
@@ -6655,18 +7050,18 @@
       <c r="C14" s="24" t="n"/>
       <c r="D14" s="24" t="n"/>
       <c r="E14" s="24" t="n"/>
-      <c r="F14" s="83" t="n"/>
-      <c r="G14" s="83" t="n"/>
-      <c r="H14" s="83" t="n"/>
-      <c r="I14" s="82" t="n"/>
-      <c r="J14" s="82" t="n"/>
-      <c r="K14" s="84">
+      <c r="F14" s="82" t="n"/>
+      <c r="G14" s="82" t="n"/>
+      <c r="H14" s="82" t="n"/>
+      <c r="I14" s="81" t="n"/>
+      <c r="J14" s="81" t="n"/>
+      <c r="K14" s="83">
         <f>IF(I14="","",I14+J14)</f>
         <v/>
       </c>
-      <c r="L14" s="82" t="n"/>
-      <c r="M14" s="82" t="n"/>
-      <c r="N14" s="84">
+      <c r="L14" s="81" t="n"/>
+      <c r="M14" s="81" t="n"/>
+      <c r="N14" s="83">
         <f>IF(K14="","",K14-M14)</f>
         <v/>
       </c>
@@ -6681,18 +7076,18 @@
       <c r="C15" s="24" t="n"/>
       <c r="D15" s="24" t="n"/>
       <c r="E15" s="24" t="n"/>
-      <c r="F15" s="83" t="n"/>
-      <c r="G15" s="83" t="n"/>
-      <c r="H15" s="83" t="n"/>
-      <c r="I15" s="82" t="n"/>
-      <c r="J15" s="82" t="n"/>
-      <c r="K15" s="84">
+      <c r="F15" s="82" t="n"/>
+      <c r="G15" s="82" t="n"/>
+      <c r="H15" s="82" t="n"/>
+      <c r="I15" s="81" t="n"/>
+      <c r="J15" s="81" t="n"/>
+      <c r="K15" s="83">
         <f>IF(I15="","",I15+J15)</f>
         <v/>
       </c>
-      <c r="L15" s="82" t="n"/>
-      <c r="M15" s="82" t="n"/>
-      <c r="N15" s="84">
+      <c r="L15" s="81" t="n"/>
+      <c r="M15" s="81" t="n"/>
+      <c r="N15" s="83">
         <f>IF(K15="","",K15-M15)</f>
         <v/>
       </c>
@@ -6707,18 +7102,18 @@
       <c r="C16" s="24" t="n"/>
       <c r="D16" s="24" t="n"/>
       <c r="E16" s="24" t="n"/>
-      <c r="F16" s="83" t="n"/>
-      <c r="G16" s="83" t="n"/>
-      <c r="H16" s="83" t="n"/>
-      <c r="I16" s="82" t="n"/>
-      <c r="J16" s="82" t="n"/>
-      <c r="K16" s="84">
+      <c r="F16" s="82" t="n"/>
+      <c r="G16" s="82" t="n"/>
+      <c r="H16" s="82" t="n"/>
+      <c r="I16" s="81" t="n"/>
+      <c r="J16" s="81" t="n"/>
+      <c r="K16" s="83">
         <f>IF(I16="","",I16+J16)</f>
         <v/>
       </c>
-      <c r="L16" s="82" t="n"/>
-      <c r="M16" s="82" t="n"/>
-      <c r="N16" s="84">
+      <c r="L16" s="81" t="n"/>
+      <c r="M16" s="81" t="n"/>
+      <c r="N16" s="83">
         <f>IF(K16="","",K16-M16)</f>
         <v/>
       </c>
@@ -6733,18 +7128,18 @@
       <c r="C17" s="24" t="n"/>
       <c r="D17" s="24" t="n"/>
       <c r="E17" s="24" t="n"/>
-      <c r="F17" s="83" t="n"/>
-      <c r="G17" s="83" t="n"/>
-      <c r="H17" s="83" t="n"/>
-      <c r="I17" s="82" t="n"/>
-      <c r="J17" s="82" t="n"/>
-      <c r="K17" s="84">
+      <c r="F17" s="82" t="n"/>
+      <c r="G17" s="82" t="n"/>
+      <c r="H17" s="82" t="n"/>
+      <c r="I17" s="81" t="n"/>
+      <c r="J17" s="81" t="n"/>
+      <c r="K17" s="83">
         <f>IF(I17="","",I17+J17)</f>
         <v/>
       </c>
-      <c r="L17" s="82" t="n"/>
-      <c r="M17" s="82" t="n"/>
-      <c r="N17" s="84">
+      <c r="L17" s="81" t="n"/>
+      <c r="M17" s="81" t="n"/>
+      <c r="N17" s="83">
         <f>IF(K17="","",K17-M17)</f>
         <v/>
       </c>
@@ -6759,18 +7154,18 @@
       <c r="C18" s="24" t="n"/>
       <c r="D18" s="24" t="n"/>
       <c r="E18" s="24" t="n"/>
-      <c r="F18" s="83" t="n"/>
-      <c r="G18" s="83" t="n"/>
-      <c r="H18" s="83" t="n"/>
-      <c r="I18" s="82" t="n"/>
-      <c r="J18" s="82" t="n"/>
-      <c r="K18" s="84">
+      <c r="F18" s="82" t="n"/>
+      <c r="G18" s="82" t="n"/>
+      <c r="H18" s="82" t="n"/>
+      <c r="I18" s="81" t="n"/>
+      <c r="J18" s="81" t="n"/>
+      <c r="K18" s="83">
         <f>IF(I18="","",I18+J18)</f>
         <v/>
       </c>
-      <c r="L18" s="82" t="n"/>
-      <c r="M18" s="82" t="n"/>
-      <c r="N18" s="84">
+      <c r="L18" s="81" t="n"/>
+      <c r="M18" s="81" t="n"/>
+      <c r="N18" s="83">
         <f>IF(K18="","",K18-M18)</f>
         <v/>
       </c>
@@ -6785,18 +7180,18 @@
       <c r="C19" s="24" t="n"/>
       <c r="D19" s="24" t="n"/>
       <c r="E19" s="24" t="n"/>
-      <c r="F19" s="83" t="n"/>
-      <c r="G19" s="83" t="n"/>
-      <c r="H19" s="83" t="n"/>
-      <c r="I19" s="82" t="n"/>
-      <c r="J19" s="82" t="n"/>
-      <c r="K19" s="84">
+      <c r="F19" s="82" t="n"/>
+      <c r="G19" s="82" t="n"/>
+      <c r="H19" s="82" t="n"/>
+      <c r="I19" s="81" t="n"/>
+      <c r="J19" s="81" t="n"/>
+      <c r="K19" s="83">
         <f>IF(I19="","",I19+J19)</f>
         <v/>
       </c>
-      <c r="L19" s="82" t="n"/>
-      <c r="M19" s="82" t="n"/>
-      <c r="N19" s="84">
+      <c r="L19" s="81" t="n"/>
+      <c r="M19" s="81" t="n"/>
+      <c r="N19" s="83">
         <f>IF(K19="","",K19-M19)</f>
         <v/>
       </c>
@@ -6811,18 +7206,18 @@
       <c r="C20" s="24" t="n"/>
       <c r="D20" s="24" t="n"/>
       <c r="E20" s="24" t="n"/>
-      <c r="F20" s="83" t="n"/>
-      <c r="G20" s="83" t="n"/>
-      <c r="H20" s="83" t="n"/>
-      <c r="I20" s="82" t="n"/>
-      <c r="J20" s="82" t="n"/>
-      <c r="K20" s="84">
+      <c r="F20" s="82" t="n"/>
+      <c r="G20" s="82" t="n"/>
+      <c r="H20" s="82" t="n"/>
+      <c r="I20" s="81" t="n"/>
+      <c r="J20" s="81" t="n"/>
+      <c r="K20" s="83">
         <f>IF(I20="","",I20+J20)</f>
         <v/>
       </c>
-      <c r="L20" s="82" t="n"/>
-      <c r="M20" s="82" t="n"/>
-      <c r="N20" s="84">
+      <c r="L20" s="81" t="n"/>
+      <c r="M20" s="81" t="n"/>
+      <c r="N20" s="83">
         <f>IF(K20="","",K20-M20)</f>
         <v/>
       </c>
@@ -6837,18 +7232,18 @@
       <c r="C21" s="24" t="n"/>
       <c r="D21" s="24" t="n"/>
       <c r="E21" s="24" t="n"/>
-      <c r="F21" s="83" t="n"/>
-      <c r="G21" s="83" t="n"/>
-      <c r="H21" s="83" t="n"/>
-      <c r="I21" s="82" t="n"/>
-      <c r="J21" s="82" t="n"/>
-      <c r="K21" s="84">
+      <c r="F21" s="82" t="n"/>
+      <c r="G21" s="82" t="n"/>
+      <c r="H21" s="82" t="n"/>
+      <c r="I21" s="81" t="n"/>
+      <c r="J21" s="81" t="n"/>
+      <c r="K21" s="83">
         <f>IF(I21="","",I21+J21)</f>
         <v/>
       </c>
-      <c r="L21" s="82" t="n"/>
-      <c r="M21" s="82" t="n"/>
-      <c r="N21" s="84">
+      <c r="L21" s="81" t="n"/>
+      <c r="M21" s="81" t="n"/>
+      <c r="N21" s="83">
         <f>IF(K21="","",K21-M21)</f>
         <v/>
       </c>
@@ -6863,18 +7258,18 @@
       <c r="C22" s="24" t="n"/>
       <c r="D22" s="24" t="n"/>
       <c r="E22" s="24" t="n"/>
-      <c r="F22" s="83" t="n"/>
-      <c r="G22" s="83" t="n"/>
-      <c r="H22" s="83" t="n"/>
-      <c r="I22" s="82" t="n"/>
-      <c r="J22" s="82" t="n"/>
-      <c r="K22" s="84">
+      <c r="F22" s="82" t="n"/>
+      <c r="G22" s="82" t="n"/>
+      <c r="H22" s="82" t="n"/>
+      <c r="I22" s="81" t="n"/>
+      <c r="J22" s="81" t="n"/>
+      <c r="K22" s="83">
         <f>IF(I22="","",I22+J22)</f>
         <v/>
       </c>
-      <c r="L22" s="82" t="n"/>
-      <c r="M22" s="82" t="n"/>
-      <c r="N22" s="84">
+      <c r="L22" s="81" t="n"/>
+      <c r="M22" s="81" t="n"/>
+      <c r="N22" s="83">
         <f>IF(K22="","",K22-M22)</f>
         <v/>
       </c>
@@ -6889,18 +7284,18 @@
       <c r="C23" s="24" t="n"/>
       <c r="D23" s="24" t="n"/>
       <c r="E23" s="24" t="n"/>
-      <c r="F23" s="83" t="n"/>
-      <c r="G23" s="83" t="n"/>
-      <c r="H23" s="83" t="n"/>
-      <c r="I23" s="82" t="n"/>
-      <c r="J23" s="82" t="n"/>
-      <c r="K23" s="84">
+      <c r="F23" s="82" t="n"/>
+      <c r="G23" s="82" t="n"/>
+      <c r="H23" s="82" t="n"/>
+      <c r="I23" s="81" t="n"/>
+      <c r="J23" s="81" t="n"/>
+      <c r="K23" s="83">
         <f>IF(I23="","",I23+J23)</f>
         <v/>
       </c>
-      <c r="L23" s="82" t="n"/>
-      <c r="M23" s="82" t="n"/>
-      <c r="N23" s="84">
+      <c r="L23" s="81" t="n"/>
+      <c r="M23" s="81" t="n"/>
+      <c r="N23" s="83">
         <f>IF(K23="","",K23-M23)</f>
         <v/>
       </c>
@@ -6915,18 +7310,18 @@
       <c r="C24" s="24" t="n"/>
       <c r="D24" s="24" t="n"/>
       <c r="E24" s="24" t="n"/>
-      <c r="F24" s="83" t="n"/>
-      <c r="G24" s="83" t="n"/>
-      <c r="H24" s="83" t="n"/>
-      <c r="I24" s="82" t="n"/>
-      <c r="J24" s="82" t="n"/>
-      <c r="K24" s="84">
+      <c r="F24" s="82" t="n"/>
+      <c r="G24" s="82" t="n"/>
+      <c r="H24" s="82" t="n"/>
+      <c r="I24" s="81" t="n"/>
+      <c r="J24" s="81" t="n"/>
+      <c r="K24" s="83">
         <f>IF(I24="","",I24+J24)</f>
         <v/>
       </c>
-      <c r="L24" s="82" t="n"/>
-      <c r="M24" s="82" t="n"/>
-      <c r="N24" s="84">
+      <c r="L24" s="81" t="n"/>
+      <c r="M24" s="81" t="n"/>
+      <c r="N24" s="83">
         <f>IF(K24="","",K24-M24)</f>
         <v/>
       </c>
@@ -7074,510 +7469,510 @@
       <c r="A5" s="24" t="n"/>
       <c r="B5" s="24" t="n"/>
       <c r="C5" s="24" t="n"/>
-      <c r="D5" s="83" t="n"/>
-      <c r="E5" s="85" t="n"/>
-      <c r="F5" s="82" t="n"/>
+      <c r="D5" s="82" t="n"/>
+      <c r="E5" s="84" t="n"/>
+      <c r="F5" s="81" t="n"/>
       <c r="G5" s="29" t="n"/>
       <c r="H5" s="29" t="n"/>
       <c r="I5" s="29" t="n"/>
       <c r="J5" s="24" t="n"/>
       <c r="K5" s="24" t="n"/>
       <c r="L5" s="24" t="n"/>
-      <c r="M5" s="83" t="n"/>
-      <c r="N5" s="82" t="n"/>
+      <c r="M5" s="82" t="n"/>
+      <c r="N5" s="81" t="n"/>
       <c r="O5" s="24" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="24" t="n"/>
       <c r="B6" s="24" t="n"/>
       <c r="C6" s="24" t="n"/>
-      <c r="D6" s="83" t="n"/>
-      <c r="E6" s="85" t="n"/>
-      <c r="F6" s="82" t="n"/>
+      <c r="D6" s="82" t="n"/>
+      <c r="E6" s="84" t="n"/>
+      <c r="F6" s="81" t="n"/>
       <c r="G6" s="29" t="n"/>
       <c r="H6" s="29" t="n"/>
       <c r="I6" s="29" t="n"/>
       <c r="J6" s="24" t="n"/>
       <c r="K6" s="24" t="n"/>
       <c r="L6" s="24" t="n"/>
-      <c r="M6" s="83" t="n"/>
-      <c r="N6" s="82" t="n"/>
+      <c r="M6" s="82" t="n"/>
+      <c r="N6" s="81" t="n"/>
       <c r="O6" s="24" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="24" t="n"/>
       <c r="B7" s="24" t="n"/>
       <c r="C7" s="24" t="n"/>
-      <c r="D7" s="83" t="n"/>
-      <c r="E7" s="85" t="n"/>
-      <c r="F7" s="82" t="n"/>
+      <c r="D7" s="82" t="n"/>
+      <c r="E7" s="84" t="n"/>
+      <c r="F7" s="81" t="n"/>
       <c r="G7" s="29" t="n"/>
       <c r="H7" s="29" t="n"/>
       <c r="I7" s="29" t="n"/>
       <c r="J7" s="24" t="n"/>
       <c r="K7" s="24" t="n"/>
       <c r="L7" s="24" t="n"/>
-      <c r="M7" s="83" t="n"/>
-      <c r="N7" s="82" t="n"/>
+      <c r="M7" s="82" t="n"/>
+      <c r="N7" s="81" t="n"/>
       <c r="O7" s="24" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="24" t="n"/>
       <c r="B8" s="24" t="n"/>
       <c r="C8" s="24" t="n"/>
-      <c r="D8" s="83" t="n"/>
-      <c r="E8" s="85" t="n"/>
-      <c r="F8" s="82" t="n"/>
+      <c r="D8" s="82" t="n"/>
+      <c r="E8" s="84" t="n"/>
+      <c r="F8" s="81" t="n"/>
       <c r="G8" s="29" t="n"/>
       <c r="H8" s="29" t="n"/>
       <c r="I8" s="29" t="n"/>
       <c r="J8" s="24" t="n"/>
       <c r="K8" s="24" t="n"/>
       <c r="L8" s="24" t="n"/>
-      <c r="M8" s="83" t="n"/>
-      <c r="N8" s="82" t="n"/>
+      <c r="M8" s="82" t="n"/>
+      <c r="N8" s="81" t="n"/>
       <c r="O8" s="24" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="24" t="n"/>
       <c r="B9" s="24" t="n"/>
       <c r="C9" s="24" t="n"/>
-      <c r="D9" s="83" t="n"/>
-      <c r="E9" s="85" t="n"/>
-      <c r="F9" s="82" t="n"/>
+      <c r="D9" s="82" t="n"/>
+      <c r="E9" s="84" t="n"/>
+      <c r="F9" s="81" t="n"/>
       <c r="G9" s="29" t="n"/>
       <c r="H9" s="29" t="n"/>
       <c r="I9" s="29" t="n"/>
       <c r="J9" s="24" t="n"/>
       <c r="K9" s="24" t="n"/>
       <c r="L9" s="24" t="n"/>
-      <c r="M9" s="83" t="n"/>
-      <c r="N9" s="82" t="n"/>
+      <c r="M9" s="82" t="n"/>
+      <c r="N9" s="81" t="n"/>
       <c r="O9" s="24" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="24" t="n"/>
       <c r="B10" s="24" t="n"/>
       <c r="C10" s="24" t="n"/>
-      <c r="D10" s="83" t="n"/>
-      <c r="E10" s="85" t="n"/>
-      <c r="F10" s="82" t="n"/>
+      <c r="D10" s="82" t="n"/>
+      <c r="E10" s="84" t="n"/>
+      <c r="F10" s="81" t="n"/>
       <c r="G10" s="29" t="n"/>
       <c r="H10" s="29" t="n"/>
       <c r="I10" s="29" t="n"/>
       <c r="J10" s="24" t="n"/>
       <c r="K10" s="24" t="n"/>
       <c r="L10" s="24" t="n"/>
-      <c r="M10" s="83" t="n"/>
-      <c r="N10" s="82" t="n"/>
+      <c r="M10" s="82" t="n"/>
+      <c r="N10" s="81" t="n"/>
       <c r="O10" s="24" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="24" t="n"/>
       <c r="B11" s="24" t="n"/>
       <c r="C11" s="24" t="n"/>
-      <c r="D11" s="83" t="n"/>
-      <c r="E11" s="85" t="n"/>
-      <c r="F11" s="82" t="n"/>
+      <c r="D11" s="82" t="n"/>
+      <c r="E11" s="84" t="n"/>
+      <c r="F11" s="81" t="n"/>
       <c r="G11" s="29" t="n"/>
       <c r="H11" s="29" t="n"/>
       <c r="I11" s="29" t="n"/>
       <c r="J11" s="24" t="n"/>
       <c r="K11" s="24" t="n"/>
       <c r="L11" s="24" t="n"/>
-      <c r="M11" s="83" t="n"/>
-      <c r="N11" s="82" t="n"/>
+      <c r="M11" s="82" t="n"/>
+      <c r="N11" s="81" t="n"/>
       <c r="O11" s="24" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="24" t="n"/>
       <c r="B12" s="24" t="n"/>
       <c r="C12" s="24" t="n"/>
-      <c r="D12" s="83" t="n"/>
-      <c r="E12" s="85" t="n"/>
-      <c r="F12" s="82" t="n"/>
+      <c r="D12" s="82" t="n"/>
+      <c r="E12" s="84" t="n"/>
+      <c r="F12" s="81" t="n"/>
       <c r="G12" s="29" t="n"/>
       <c r="H12" s="29" t="n"/>
       <c r="I12" s="29" t="n"/>
       <c r="J12" s="24" t="n"/>
       <c r="K12" s="24" t="n"/>
       <c r="L12" s="24" t="n"/>
-      <c r="M12" s="83" t="n"/>
-      <c r="N12" s="82" t="n"/>
+      <c r="M12" s="82" t="n"/>
+      <c r="N12" s="81" t="n"/>
       <c r="O12" s="24" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="24" t="n"/>
       <c r="B13" s="24" t="n"/>
       <c r="C13" s="24" t="n"/>
-      <c r="D13" s="83" t="n"/>
-      <c r="E13" s="85" t="n"/>
-      <c r="F13" s="82" t="n"/>
+      <c r="D13" s="82" t="n"/>
+      <c r="E13" s="84" t="n"/>
+      <c r="F13" s="81" t="n"/>
       <c r="G13" s="29" t="n"/>
       <c r="H13" s="29" t="n"/>
       <c r="I13" s="29" t="n"/>
       <c r="J13" s="24" t="n"/>
       <c r="K13" s="24" t="n"/>
       <c r="L13" s="24" t="n"/>
-      <c r="M13" s="83" t="n"/>
-      <c r="N13" s="82" t="n"/>
+      <c r="M13" s="82" t="n"/>
+      <c r="N13" s="81" t="n"/>
       <c r="O13" s="24" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="24" t="n"/>
       <c r="B14" s="24" t="n"/>
       <c r="C14" s="24" t="n"/>
-      <c r="D14" s="83" t="n"/>
-      <c r="E14" s="85" t="n"/>
-      <c r="F14" s="82" t="n"/>
+      <c r="D14" s="82" t="n"/>
+      <c r="E14" s="84" t="n"/>
+      <c r="F14" s="81" t="n"/>
       <c r="G14" s="29" t="n"/>
       <c r="H14" s="29" t="n"/>
       <c r="I14" s="29" t="n"/>
       <c r="J14" s="24" t="n"/>
       <c r="K14" s="24" t="n"/>
       <c r="L14" s="24" t="n"/>
-      <c r="M14" s="83" t="n"/>
-      <c r="N14" s="82" t="n"/>
+      <c r="M14" s="82" t="n"/>
+      <c r="N14" s="81" t="n"/>
       <c r="O14" s="24" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="24" t="n"/>
       <c r="B15" s="24" t="n"/>
       <c r="C15" s="24" t="n"/>
-      <c r="D15" s="83" t="n"/>
-      <c r="E15" s="85" t="n"/>
-      <c r="F15" s="82" t="n"/>
+      <c r="D15" s="82" t="n"/>
+      <c r="E15" s="84" t="n"/>
+      <c r="F15" s="81" t="n"/>
       <c r="G15" s="29" t="n"/>
       <c r="H15" s="29" t="n"/>
       <c r="I15" s="29" t="n"/>
       <c r="J15" s="24" t="n"/>
       <c r="K15" s="24" t="n"/>
       <c r="L15" s="24" t="n"/>
-      <c r="M15" s="83" t="n"/>
-      <c r="N15" s="82" t="n"/>
+      <c r="M15" s="82" t="n"/>
+      <c r="N15" s="81" t="n"/>
       <c r="O15" s="24" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="24" t="n"/>
       <c r="B16" s="24" t="n"/>
       <c r="C16" s="24" t="n"/>
-      <c r="D16" s="83" t="n"/>
-      <c r="E16" s="85" t="n"/>
-      <c r="F16" s="82" t="n"/>
+      <c r="D16" s="82" t="n"/>
+      <c r="E16" s="84" t="n"/>
+      <c r="F16" s="81" t="n"/>
       <c r="G16" s="29" t="n"/>
       <c r="H16" s="29" t="n"/>
       <c r="I16" s="29" t="n"/>
       <c r="J16" s="24" t="n"/>
       <c r="K16" s="24" t="n"/>
       <c r="L16" s="24" t="n"/>
-      <c r="M16" s="83" t="n"/>
-      <c r="N16" s="82" t="n"/>
+      <c r="M16" s="82" t="n"/>
+      <c r="N16" s="81" t="n"/>
       <c r="O16" s="24" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="24" t="n"/>
       <c r="B17" s="24" t="n"/>
       <c r="C17" s="24" t="n"/>
-      <c r="D17" s="83" t="n"/>
-      <c r="E17" s="85" t="n"/>
-      <c r="F17" s="82" t="n"/>
+      <c r="D17" s="82" t="n"/>
+      <c r="E17" s="84" t="n"/>
+      <c r="F17" s="81" t="n"/>
       <c r="G17" s="29" t="n"/>
       <c r="H17" s="29" t="n"/>
       <c r="I17" s="29" t="n"/>
       <c r="J17" s="24" t="n"/>
       <c r="K17" s="24" t="n"/>
       <c r="L17" s="24" t="n"/>
-      <c r="M17" s="83" t="n"/>
-      <c r="N17" s="82" t="n"/>
+      <c r="M17" s="82" t="n"/>
+      <c r="N17" s="81" t="n"/>
       <c r="O17" s="24" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="24" t="n"/>
       <c r="B18" s="24" t="n"/>
       <c r="C18" s="24" t="n"/>
-      <c r="D18" s="83" t="n"/>
-      <c r="E18" s="85" t="n"/>
-      <c r="F18" s="82" t="n"/>
+      <c r="D18" s="82" t="n"/>
+      <c r="E18" s="84" t="n"/>
+      <c r="F18" s="81" t="n"/>
       <c r="G18" s="29" t="n"/>
       <c r="H18" s="29" t="n"/>
       <c r="I18" s="29" t="n"/>
       <c r="J18" s="24" t="n"/>
       <c r="K18" s="24" t="n"/>
       <c r="L18" s="24" t="n"/>
-      <c r="M18" s="83" t="n"/>
-      <c r="N18" s="82" t="n"/>
+      <c r="M18" s="82" t="n"/>
+      <c r="N18" s="81" t="n"/>
       <c r="O18" s="24" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="24" t="n"/>
       <c r="B19" s="24" t="n"/>
       <c r="C19" s="24" t="n"/>
-      <c r="D19" s="83" t="n"/>
-      <c r="E19" s="85" t="n"/>
-      <c r="F19" s="82" t="n"/>
+      <c r="D19" s="82" t="n"/>
+      <c r="E19" s="84" t="n"/>
+      <c r="F19" s="81" t="n"/>
       <c r="G19" s="29" t="n"/>
       <c r="H19" s="29" t="n"/>
       <c r="I19" s="29" t="n"/>
       <c r="J19" s="24" t="n"/>
       <c r="K19" s="24" t="n"/>
       <c r="L19" s="24" t="n"/>
-      <c r="M19" s="83" t="n"/>
-      <c r="N19" s="82" t="n"/>
+      <c r="M19" s="82" t="n"/>
+      <c r="N19" s="81" t="n"/>
       <c r="O19" s="24" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="24" t="n"/>
       <c r="B20" s="24" t="n"/>
       <c r="C20" s="24" t="n"/>
-      <c r="D20" s="83" t="n"/>
-      <c r="E20" s="85" t="n"/>
-      <c r="F20" s="82" t="n"/>
+      <c r="D20" s="82" t="n"/>
+      <c r="E20" s="84" t="n"/>
+      <c r="F20" s="81" t="n"/>
       <c r="G20" s="29" t="n"/>
       <c r="H20" s="29" t="n"/>
       <c r="I20" s="29" t="n"/>
       <c r="J20" s="24" t="n"/>
       <c r="K20" s="24" t="n"/>
       <c r="L20" s="24" t="n"/>
-      <c r="M20" s="83" t="n"/>
-      <c r="N20" s="82" t="n"/>
+      <c r="M20" s="82" t="n"/>
+      <c r="N20" s="81" t="n"/>
       <c r="O20" s="24" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="24" t="n"/>
       <c r="B21" s="24" t="n"/>
       <c r="C21" s="24" t="n"/>
-      <c r="D21" s="83" t="n"/>
-      <c r="E21" s="85" t="n"/>
-      <c r="F21" s="82" t="n"/>
+      <c r="D21" s="82" t="n"/>
+      <c r="E21" s="84" t="n"/>
+      <c r="F21" s="81" t="n"/>
       <c r="G21" s="29" t="n"/>
       <c r="H21" s="29" t="n"/>
       <c r="I21" s="29" t="n"/>
       <c r="J21" s="24" t="n"/>
       <c r="K21" s="24" t="n"/>
       <c r="L21" s="24" t="n"/>
-      <c r="M21" s="83" t="n"/>
-      <c r="N21" s="82" t="n"/>
+      <c r="M21" s="82" t="n"/>
+      <c r="N21" s="81" t="n"/>
       <c r="O21" s="24" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="24" t="n"/>
       <c r="B22" s="24" t="n"/>
       <c r="C22" s="24" t="n"/>
-      <c r="D22" s="83" t="n"/>
-      <c r="E22" s="85" t="n"/>
-      <c r="F22" s="82" t="n"/>
+      <c r="D22" s="82" t="n"/>
+      <c r="E22" s="84" t="n"/>
+      <c r="F22" s="81" t="n"/>
       <c r="G22" s="29" t="n"/>
       <c r="H22" s="29" t="n"/>
       <c r="I22" s="29" t="n"/>
       <c r="J22" s="24" t="n"/>
       <c r="K22" s="24" t="n"/>
       <c r="L22" s="24" t="n"/>
-      <c r="M22" s="83" t="n"/>
-      <c r="N22" s="82" t="n"/>
+      <c r="M22" s="82" t="n"/>
+      <c r="N22" s="81" t="n"/>
       <c r="O22" s="24" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="24" t="n"/>
       <c r="B23" s="24" t="n"/>
       <c r="C23" s="24" t="n"/>
-      <c r="D23" s="83" t="n"/>
-      <c r="E23" s="85" t="n"/>
-      <c r="F23" s="82" t="n"/>
+      <c r="D23" s="82" t="n"/>
+      <c r="E23" s="84" t="n"/>
+      <c r="F23" s="81" t="n"/>
       <c r="G23" s="29" t="n"/>
       <c r="H23" s="29" t="n"/>
       <c r="I23" s="29" t="n"/>
       <c r="J23" s="24" t="n"/>
       <c r="K23" s="24" t="n"/>
       <c r="L23" s="24" t="n"/>
-      <c r="M23" s="83" t="n"/>
-      <c r="N23" s="82" t="n"/>
+      <c r="M23" s="82" t="n"/>
+      <c r="N23" s="81" t="n"/>
       <c r="O23" s="24" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="24" t="n"/>
       <c r="B24" s="24" t="n"/>
       <c r="C24" s="24" t="n"/>
-      <c r="D24" s="83" t="n"/>
-      <c r="E24" s="85" t="n"/>
-      <c r="F24" s="82" t="n"/>
+      <c r="D24" s="82" t="n"/>
+      <c r="E24" s="84" t="n"/>
+      <c r="F24" s="81" t="n"/>
       <c r="G24" s="29" t="n"/>
       <c r="H24" s="29" t="n"/>
       <c r="I24" s="29" t="n"/>
       <c r="J24" s="24" t="n"/>
       <c r="K24" s="24" t="n"/>
       <c r="L24" s="24" t="n"/>
-      <c r="M24" s="83" t="n"/>
-      <c r="N24" s="82" t="n"/>
+      <c r="M24" s="82" t="n"/>
+      <c r="N24" s="81" t="n"/>
       <c r="O24" s="24" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="24" t="n"/>
       <c r="B25" s="24" t="n"/>
       <c r="C25" s="24" t="n"/>
-      <c r="D25" s="83" t="n"/>
-      <c r="E25" s="85" t="n"/>
-      <c r="F25" s="82" t="n"/>
+      <c r="D25" s="82" t="n"/>
+      <c r="E25" s="84" t="n"/>
+      <c r="F25" s="81" t="n"/>
       <c r="G25" s="29" t="n"/>
       <c r="H25" s="29" t="n"/>
       <c r="I25" s="29" t="n"/>
       <c r="J25" s="24" t="n"/>
       <c r="K25" s="24" t="n"/>
       <c r="L25" s="24" t="n"/>
-      <c r="M25" s="83" t="n"/>
-      <c r="N25" s="82" t="n"/>
+      <c r="M25" s="82" t="n"/>
+      <c r="N25" s="81" t="n"/>
       <c r="O25" s="24" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="n"/>
       <c r="B26" s="24" t="n"/>
       <c r="C26" s="24" t="n"/>
-      <c r="D26" s="83" t="n"/>
-      <c r="E26" s="85" t="n"/>
-      <c r="F26" s="82" t="n"/>
+      <c r="D26" s="82" t="n"/>
+      <c r="E26" s="84" t="n"/>
+      <c r="F26" s="81" t="n"/>
       <c r="G26" s="29" t="n"/>
       <c r="H26" s="29" t="n"/>
       <c r="I26" s="29" t="n"/>
       <c r="J26" s="24" t="n"/>
       <c r="K26" s="24" t="n"/>
       <c r="L26" s="24" t="n"/>
-      <c r="M26" s="83" t="n"/>
-      <c r="N26" s="82" t="n"/>
+      <c r="M26" s="82" t="n"/>
+      <c r="N26" s="81" t="n"/>
       <c r="O26" s="24" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="24" t="n"/>
       <c r="B27" s="24" t="n"/>
       <c r="C27" s="24" t="n"/>
-      <c r="D27" s="83" t="n"/>
-      <c r="E27" s="85" t="n"/>
-      <c r="F27" s="82" t="n"/>
+      <c r="D27" s="82" t="n"/>
+      <c r="E27" s="84" t="n"/>
+      <c r="F27" s="81" t="n"/>
       <c r="G27" s="29" t="n"/>
       <c r="H27" s="29" t="n"/>
       <c r="I27" s="29" t="n"/>
       <c r="J27" s="24" t="n"/>
       <c r="K27" s="24" t="n"/>
       <c r="L27" s="24" t="n"/>
-      <c r="M27" s="83" t="n"/>
-      <c r="N27" s="82" t="n"/>
+      <c r="M27" s="82" t="n"/>
+      <c r="N27" s="81" t="n"/>
       <c r="O27" s="24" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="24" t="n"/>
       <c r="B28" s="24" t="n"/>
       <c r="C28" s="24" t="n"/>
-      <c r="D28" s="83" t="n"/>
-      <c r="E28" s="85" t="n"/>
-      <c r="F28" s="82" t="n"/>
+      <c r="D28" s="82" t="n"/>
+      <c r="E28" s="84" t="n"/>
+      <c r="F28" s="81" t="n"/>
       <c r="G28" s="29" t="n"/>
       <c r="H28" s="29" t="n"/>
       <c r="I28" s="29" t="n"/>
       <c r="J28" s="24" t="n"/>
       <c r="K28" s="24" t="n"/>
       <c r="L28" s="24" t="n"/>
-      <c r="M28" s="83" t="n"/>
-      <c r="N28" s="82" t="n"/>
+      <c r="M28" s="82" t="n"/>
+      <c r="N28" s="81" t="n"/>
       <c r="O28" s="24" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="24" t="n"/>
       <c r="B29" s="24" t="n"/>
       <c r="C29" s="24" t="n"/>
-      <c r="D29" s="83" t="n"/>
-      <c r="E29" s="85" t="n"/>
-      <c r="F29" s="82" t="n"/>
+      <c r="D29" s="82" t="n"/>
+      <c r="E29" s="84" t="n"/>
+      <c r="F29" s="81" t="n"/>
       <c r="G29" s="29" t="n"/>
       <c r="H29" s="29" t="n"/>
       <c r="I29" s="29" t="n"/>
       <c r="J29" s="24" t="n"/>
       <c r="K29" s="24" t="n"/>
       <c r="L29" s="24" t="n"/>
-      <c r="M29" s="83" t="n"/>
-      <c r="N29" s="82" t="n"/>
+      <c r="M29" s="82" t="n"/>
+      <c r="N29" s="81" t="n"/>
       <c r="O29" s="24" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="24" t="n"/>
       <c r="B30" s="24" t="n"/>
       <c r="C30" s="24" t="n"/>
-      <c r="D30" s="83" t="n"/>
-      <c r="E30" s="85" t="n"/>
-      <c r="F30" s="82" t="n"/>
+      <c r="D30" s="82" t="n"/>
+      <c r="E30" s="84" t="n"/>
+      <c r="F30" s="81" t="n"/>
       <c r="G30" s="29" t="n"/>
       <c r="H30" s="29" t="n"/>
       <c r="I30" s="29" t="n"/>
       <c r="J30" s="24" t="n"/>
       <c r="K30" s="24" t="n"/>
       <c r="L30" s="24" t="n"/>
-      <c r="M30" s="83" t="n"/>
-      <c r="N30" s="82" t="n"/>
+      <c r="M30" s="82" t="n"/>
+      <c r="N30" s="81" t="n"/>
       <c r="O30" s="24" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="24" t="n"/>
       <c r="B31" s="24" t="n"/>
       <c r="C31" s="24" t="n"/>
-      <c r="D31" s="83" t="n"/>
-      <c r="E31" s="85" t="n"/>
-      <c r="F31" s="82" t="n"/>
+      <c r="D31" s="82" t="n"/>
+      <c r="E31" s="84" t="n"/>
+      <c r="F31" s="81" t="n"/>
       <c r="G31" s="29" t="n"/>
       <c r="H31" s="29" t="n"/>
       <c r="I31" s="29" t="n"/>
       <c r="J31" s="24" t="n"/>
       <c r="K31" s="24" t="n"/>
       <c r="L31" s="24" t="n"/>
-      <c r="M31" s="83" t="n"/>
-      <c r="N31" s="82" t="n"/>
+      <c r="M31" s="82" t="n"/>
+      <c r="N31" s="81" t="n"/>
       <c r="O31" s="24" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="24" t="n"/>
       <c r="B32" s="24" t="n"/>
       <c r="C32" s="24" t="n"/>
-      <c r="D32" s="83" t="n"/>
-      <c r="E32" s="85" t="n"/>
-      <c r="F32" s="82" t="n"/>
+      <c r="D32" s="82" t="n"/>
+      <c r="E32" s="84" t="n"/>
+      <c r="F32" s="81" t="n"/>
       <c r="G32" s="29" t="n"/>
       <c r="H32" s="29" t="n"/>
       <c r="I32" s="29" t="n"/>
       <c r="J32" s="24" t="n"/>
       <c r="K32" s="24" t="n"/>
       <c r="L32" s="24" t="n"/>
-      <c r="M32" s="83" t="n"/>
-      <c r="N32" s="82" t="n"/>
+      <c r="M32" s="82" t="n"/>
+      <c r="N32" s="81" t="n"/>
       <c r="O32" s="24" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="24" t="n"/>
       <c r="B33" s="24" t="n"/>
       <c r="C33" s="24" t="n"/>
-      <c r="D33" s="83" t="n"/>
-      <c r="E33" s="85" t="n"/>
-      <c r="F33" s="82" t="n"/>
+      <c r="D33" s="82" t="n"/>
+      <c r="E33" s="84" t="n"/>
+      <c r="F33" s="81" t="n"/>
       <c r="G33" s="29" t="n"/>
       <c r="H33" s="29" t="n"/>
       <c r="I33" s="29" t="n"/>
       <c r="J33" s="24" t="n"/>
       <c r="K33" s="24" t="n"/>
       <c r="L33" s="24" t="n"/>
-      <c r="M33" s="83" t="n"/>
-      <c r="N33" s="82" t="n"/>
+      <c r="M33" s="82" t="n"/>
+      <c r="N33" s="81" t="n"/>
       <c r="O33" s="24" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="24" t="n"/>
       <c r="B34" s="24" t="n"/>
       <c r="C34" s="24" t="n"/>
-      <c r="D34" s="83" t="n"/>
-      <c r="E34" s="85" t="n"/>
-      <c r="F34" s="82" t="n"/>
+      <c r="D34" s="82" t="n"/>
+      <c r="E34" s="84" t="n"/>
+      <c r="F34" s="81" t="n"/>
       <c r="G34" s="29" t="n"/>
       <c r="H34" s="29" t="n"/>
       <c r="I34" s="29" t="n"/>
       <c r="J34" s="24" t="n"/>
       <c r="K34" s="24" t="n"/>
       <c r="L34" s="24" t="n"/>
-      <c r="M34" s="83" t="n"/>
-      <c r="N34" s="82" t="n"/>
+      <c r="M34" s="82" t="n"/>
+      <c r="N34" s="81" t="n"/>
       <c r="O34" s="24" t="n"/>
     </row>
   </sheetData>
@@ -7715,19 +8110,19 @@
     </row>
     <row r="5">
       <c r="A5" s="24" t="n"/>
-      <c r="B5" s="83" t="n"/>
+      <c r="B5" s="82" t="n"/>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="24" t="n"/>
       <c r="E5" s="24" t="n"/>
       <c r="F5" s="29" t="n"/>
-      <c r="G5" s="82" t="n"/>
-      <c r="H5" s="82" t="n"/>
-      <c r="I5" s="82" t="n"/>
-      <c r="J5" s="84">
+      <c r="G5" s="81" t="n"/>
+      <c r="H5" s="81" t="n"/>
+      <c r="I5" s="81" t="n"/>
+      <c r="J5" s="83">
         <f>IF(COUNTA(G5:I5)=0,"",SUM(G5:I5))</f>
         <v/>
       </c>
-      <c r="K5" s="86" t="n"/>
+      <c r="K5" s="85" t="n"/>
       <c r="L5" s="24" t="n"/>
       <c r="M5" s="24" t="n"/>
       <c r="N5" s="24" t="n"/>
@@ -7735,19 +8130,19 @@
     </row>
     <row r="6">
       <c r="A6" s="24" t="n"/>
-      <c r="B6" s="83" t="n"/>
+      <c r="B6" s="82" t="n"/>
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="24" t="n"/>
       <c r="E6" s="24" t="n"/>
       <c r="F6" s="29" t="n"/>
-      <c r="G6" s="82" t="n"/>
-      <c r="H6" s="82" t="n"/>
-      <c r="I6" s="82" t="n"/>
-      <c r="J6" s="84">
+      <c r="G6" s="81" t="n"/>
+      <c r="H6" s="81" t="n"/>
+      <c r="I6" s="81" t="n"/>
+      <c r="J6" s="83">
         <f>IF(COUNTA(G6:I6)=0,"",SUM(G6:I6))</f>
         <v/>
       </c>
-      <c r="K6" s="86" t="n"/>
+      <c r="K6" s="85" t="n"/>
       <c r="L6" s="24" t="n"/>
       <c r="M6" s="24" t="n"/>
       <c r="N6" s="24" t="n"/>
@@ -7755,19 +8150,19 @@
     </row>
     <row r="7">
       <c r="A7" s="24" t="n"/>
-      <c r="B7" s="83" t="n"/>
+      <c r="B7" s="82" t="n"/>
       <c r="C7" s="24" t="n"/>
       <c r="D7" s="24" t="n"/>
       <c r="E7" s="24" t="n"/>
       <c r="F7" s="29" t="n"/>
-      <c r="G7" s="82" t="n"/>
-      <c r="H7" s="82" t="n"/>
-      <c r="I7" s="82" t="n"/>
-      <c r="J7" s="84">
+      <c r="G7" s="81" t="n"/>
+      <c r="H7" s="81" t="n"/>
+      <c r="I7" s="81" t="n"/>
+      <c r="J7" s="83">
         <f>IF(COUNTA(G7:I7)=0,"",SUM(G7:I7))</f>
         <v/>
       </c>
-      <c r="K7" s="86" t="n"/>
+      <c r="K7" s="85" t="n"/>
       <c r="L7" s="24" t="n"/>
       <c r="M7" s="24" t="n"/>
       <c r="N7" s="24" t="n"/>
@@ -7775,19 +8170,19 @@
     </row>
     <row r="8">
       <c r="A8" s="24" t="n"/>
-      <c r="B8" s="83" t="n"/>
+      <c r="B8" s="82" t="n"/>
       <c r="C8" s="24" t="n"/>
       <c r="D8" s="24" t="n"/>
       <c r="E8" s="24" t="n"/>
       <c r="F8" s="29" t="n"/>
-      <c r="G8" s="82" t="n"/>
-      <c r="H8" s="82" t="n"/>
-      <c r="I8" s="82" t="n"/>
-      <c r="J8" s="84">
+      <c r="G8" s="81" t="n"/>
+      <c r="H8" s="81" t="n"/>
+      <c r="I8" s="81" t="n"/>
+      <c r="J8" s="83">
         <f>IF(COUNTA(G8:I8)=0,"",SUM(G8:I8))</f>
         <v/>
       </c>
-      <c r="K8" s="86" t="n"/>
+      <c r="K8" s="85" t="n"/>
       <c r="L8" s="24" t="n"/>
       <c r="M8" s="24" t="n"/>
       <c r="N8" s="24" t="n"/>
@@ -7795,19 +8190,19 @@
     </row>
     <row r="9">
       <c r="A9" s="24" t="n"/>
-      <c r="B9" s="83" t="n"/>
+      <c r="B9" s="82" t="n"/>
       <c r="C9" s="24" t="n"/>
       <c r="D9" s="24" t="n"/>
       <c r="E9" s="24" t="n"/>
       <c r="F9" s="29" t="n"/>
-      <c r="G9" s="82" t="n"/>
-      <c r="H9" s="82" t="n"/>
-      <c r="I9" s="82" t="n"/>
-      <c r="J9" s="84">
+      <c r="G9" s="81" t="n"/>
+      <c r="H9" s="81" t="n"/>
+      <c r="I9" s="81" t="n"/>
+      <c r="J9" s="83">
         <f>IF(COUNTA(G9:I9)=0,"",SUM(G9:I9))</f>
         <v/>
       </c>
-      <c r="K9" s="86" t="n"/>
+      <c r="K9" s="85" t="n"/>
       <c r="L9" s="24" t="n"/>
       <c r="M9" s="24" t="n"/>
       <c r="N9" s="24" t="n"/>
@@ -7815,19 +8210,19 @@
     </row>
     <row r="10">
       <c r="A10" s="24" t="n"/>
-      <c r="B10" s="83" t="n"/>
+      <c r="B10" s="82" t="n"/>
       <c r="C10" s="24" t="n"/>
       <c r="D10" s="24" t="n"/>
       <c r="E10" s="24" t="n"/>
       <c r="F10" s="29" t="n"/>
-      <c r="G10" s="82" t="n"/>
-      <c r="H10" s="82" t="n"/>
-      <c r="I10" s="82" t="n"/>
-      <c r="J10" s="84">
+      <c r="G10" s="81" t="n"/>
+      <c r="H10" s="81" t="n"/>
+      <c r="I10" s="81" t="n"/>
+      <c r="J10" s="83">
         <f>IF(COUNTA(G10:I10)=0,"",SUM(G10:I10))</f>
         <v/>
       </c>
-      <c r="K10" s="86" t="n"/>
+      <c r="K10" s="85" t="n"/>
       <c r="L10" s="24" t="n"/>
       <c r="M10" s="24" t="n"/>
       <c r="N10" s="24" t="n"/>
@@ -7835,19 +8230,19 @@
     </row>
     <row r="11">
       <c r="A11" s="24" t="n"/>
-      <c r="B11" s="83" t="n"/>
+      <c r="B11" s="82" t="n"/>
       <c r="C11" s="24" t="n"/>
       <c r="D11" s="24" t="n"/>
       <c r="E11" s="24" t="n"/>
       <c r="F11" s="29" t="n"/>
-      <c r="G11" s="82" t="n"/>
-      <c r="H11" s="82" t="n"/>
-      <c r="I11" s="82" t="n"/>
-      <c r="J11" s="84">
+      <c r="G11" s="81" t="n"/>
+      <c r="H11" s="81" t="n"/>
+      <c r="I11" s="81" t="n"/>
+      <c r="J11" s="83">
         <f>IF(COUNTA(G11:I11)=0,"",SUM(G11:I11))</f>
         <v/>
       </c>
-      <c r="K11" s="86" t="n"/>
+      <c r="K11" s="85" t="n"/>
       <c r="L11" s="24" t="n"/>
       <c r="M11" s="24" t="n"/>
       <c r="N11" s="24" t="n"/>
@@ -7855,19 +8250,19 @@
     </row>
     <row r="12">
       <c r="A12" s="24" t="n"/>
-      <c r="B12" s="83" t="n"/>
+      <c r="B12" s="82" t="n"/>
       <c r="C12" s="24" t="n"/>
       <c r="D12" s="24" t="n"/>
       <c r="E12" s="24" t="n"/>
       <c r="F12" s="29" t="n"/>
-      <c r="G12" s="82" t="n"/>
-      <c r="H12" s="82" t="n"/>
-      <c r="I12" s="82" t="n"/>
-      <c r="J12" s="84">
+      <c r="G12" s="81" t="n"/>
+      <c r="H12" s="81" t="n"/>
+      <c r="I12" s="81" t="n"/>
+      <c r="J12" s="83">
         <f>IF(COUNTA(G12:I12)=0,"",SUM(G12:I12))</f>
         <v/>
       </c>
-      <c r="K12" s="86" t="n"/>
+      <c r="K12" s="85" t="n"/>
       <c r="L12" s="24" t="n"/>
       <c r="M12" s="24" t="n"/>
       <c r="N12" s="24" t="n"/>
@@ -7875,19 +8270,19 @@
     </row>
     <row r="13">
       <c r="A13" s="24" t="n"/>
-      <c r="B13" s="83" t="n"/>
+      <c r="B13" s="82" t="n"/>
       <c r="C13" s="24" t="n"/>
       <c r="D13" s="24" t="n"/>
       <c r="E13" s="24" t="n"/>
       <c r="F13" s="29" t="n"/>
-      <c r="G13" s="82" t="n"/>
-      <c r="H13" s="82" t="n"/>
-      <c r="I13" s="82" t="n"/>
-      <c r="J13" s="84">
+      <c r="G13" s="81" t="n"/>
+      <c r="H13" s="81" t="n"/>
+      <c r="I13" s="81" t="n"/>
+      <c r="J13" s="83">
         <f>IF(COUNTA(G13:I13)=0,"",SUM(G13:I13))</f>
         <v/>
       </c>
-      <c r="K13" s="86" t="n"/>
+      <c r="K13" s="85" t="n"/>
       <c r="L13" s="24" t="n"/>
       <c r="M13" s="24" t="n"/>
       <c r="N13" s="24" t="n"/>
@@ -7895,19 +8290,19 @@
     </row>
     <row r="14">
       <c r="A14" s="24" t="n"/>
-      <c r="B14" s="83" t="n"/>
+      <c r="B14" s="82" t="n"/>
       <c r="C14" s="24" t="n"/>
       <c r="D14" s="24" t="n"/>
       <c r="E14" s="24" t="n"/>
       <c r="F14" s="29" t="n"/>
-      <c r="G14" s="82" t="n"/>
-      <c r="H14" s="82" t="n"/>
-      <c r="I14" s="82" t="n"/>
-      <c r="J14" s="84">
+      <c r="G14" s="81" t="n"/>
+      <c r="H14" s="81" t="n"/>
+      <c r="I14" s="81" t="n"/>
+      <c r="J14" s="83">
         <f>IF(COUNTA(G14:I14)=0,"",SUM(G14:I14))</f>
         <v/>
       </c>
-      <c r="K14" s="86" t="n"/>
+      <c r="K14" s="85" t="n"/>
       <c r="L14" s="24" t="n"/>
       <c r="M14" s="24" t="n"/>
       <c r="N14" s="24" t="n"/>
@@ -7915,19 +8310,19 @@
     </row>
     <row r="15">
       <c r="A15" s="24" t="n"/>
-      <c r="B15" s="83" t="n"/>
+      <c r="B15" s="82" t="n"/>
       <c r="C15" s="24" t="n"/>
       <c r="D15" s="24" t="n"/>
       <c r="E15" s="24" t="n"/>
       <c r="F15" s="29" t="n"/>
-      <c r="G15" s="82" t="n"/>
-      <c r="H15" s="82" t="n"/>
-      <c r="I15" s="82" t="n"/>
-      <c r="J15" s="84">
+      <c r="G15" s="81" t="n"/>
+      <c r="H15" s="81" t="n"/>
+      <c r="I15" s="81" t="n"/>
+      <c r="J15" s="83">
         <f>IF(COUNTA(G15:I15)=0,"",SUM(G15:I15))</f>
         <v/>
       </c>
-      <c r="K15" s="86" t="n"/>
+      <c r="K15" s="85" t="n"/>
       <c r="L15" s="24" t="n"/>
       <c r="M15" s="24" t="n"/>
       <c r="N15" s="24" t="n"/>
@@ -7935,19 +8330,19 @@
     </row>
     <row r="16">
       <c r="A16" s="24" t="n"/>
-      <c r="B16" s="83" t="n"/>
+      <c r="B16" s="82" t="n"/>
       <c r="C16" s="24" t="n"/>
       <c r="D16" s="24" t="n"/>
       <c r="E16" s="24" t="n"/>
       <c r="F16" s="29" t="n"/>
-      <c r="G16" s="82" t="n"/>
-      <c r="H16" s="82" t="n"/>
-      <c r="I16" s="82" t="n"/>
-      <c r="J16" s="84">
+      <c r="G16" s="81" t="n"/>
+      <c r="H16" s="81" t="n"/>
+      <c r="I16" s="81" t="n"/>
+      <c r="J16" s="83">
         <f>IF(COUNTA(G16:I16)=0,"",SUM(G16:I16))</f>
         <v/>
       </c>
-      <c r="K16" s="86" t="n"/>
+      <c r="K16" s="85" t="n"/>
       <c r="L16" s="24" t="n"/>
       <c r="M16" s="24" t="n"/>
       <c r="N16" s="24" t="n"/>
@@ -7955,19 +8350,19 @@
     </row>
     <row r="17">
       <c r="A17" s="24" t="n"/>
-      <c r="B17" s="83" t="n"/>
+      <c r="B17" s="82" t="n"/>
       <c r="C17" s="24" t="n"/>
       <c r="D17" s="24" t="n"/>
       <c r="E17" s="24" t="n"/>
       <c r="F17" s="29" t="n"/>
-      <c r="G17" s="82" t="n"/>
-      <c r="H17" s="82" t="n"/>
-      <c r="I17" s="82" t="n"/>
-      <c r="J17" s="84">
+      <c r="G17" s="81" t="n"/>
+      <c r="H17" s="81" t="n"/>
+      <c r="I17" s="81" t="n"/>
+      <c r="J17" s="83">
         <f>IF(COUNTA(G17:I17)=0,"",SUM(G17:I17))</f>
         <v/>
       </c>
-      <c r="K17" s="86" t="n"/>
+      <c r="K17" s="85" t="n"/>
       <c r="L17" s="24" t="n"/>
       <c r="M17" s="24" t="n"/>
       <c r="N17" s="24" t="n"/>
@@ -7975,19 +8370,19 @@
     </row>
     <row r="18">
       <c r="A18" s="24" t="n"/>
-      <c r="B18" s="83" t="n"/>
+      <c r="B18" s="82" t="n"/>
       <c r="C18" s="24" t="n"/>
       <c r="D18" s="24" t="n"/>
       <c r="E18" s="24" t="n"/>
       <c r="F18" s="29" t="n"/>
-      <c r="G18" s="82" t="n"/>
-      <c r="H18" s="82" t="n"/>
-      <c r="I18" s="82" t="n"/>
-      <c r="J18" s="84">
+      <c r="G18" s="81" t="n"/>
+      <c r="H18" s="81" t="n"/>
+      <c r="I18" s="81" t="n"/>
+      <c r="J18" s="83">
         <f>IF(COUNTA(G18:I18)=0,"",SUM(G18:I18))</f>
         <v/>
       </c>
-      <c r="K18" s="86" t="n"/>
+      <c r="K18" s="85" t="n"/>
       <c r="L18" s="24" t="n"/>
       <c r="M18" s="24" t="n"/>
       <c r="N18" s="24" t="n"/>
@@ -7995,19 +8390,19 @@
     </row>
     <row r="19">
       <c r="A19" s="24" t="n"/>
-      <c r="B19" s="83" t="n"/>
+      <c r="B19" s="82" t="n"/>
       <c r="C19" s="24" t="n"/>
       <c r="D19" s="24" t="n"/>
       <c r="E19" s="24" t="n"/>
       <c r="F19" s="29" t="n"/>
-      <c r="G19" s="82" t="n"/>
-      <c r="H19" s="82" t="n"/>
-      <c r="I19" s="82" t="n"/>
-      <c r="J19" s="84">
+      <c r="G19" s="81" t="n"/>
+      <c r="H19" s="81" t="n"/>
+      <c r="I19" s="81" t="n"/>
+      <c r="J19" s="83">
         <f>IF(COUNTA(G19:I19)=0,"",SUM(G19:I19))</f>
         <v/>
       </c>
-      <c r="K19" s="86" t="n"/>
+      <c r="K19" s="85" t="n"/>
       <c r="L19" s="24" t="n"/>
       <c r="M19" s="24" t="n"/>
       <c r="N19" s="24" t="n"/>
@@ -8015,19 +8410,19 @@
     </row>
     <row r="20">
       <c r="A20" s="24" t="n"/>
-      <c r="B20" s="83" t="n"/>
+      <c r="B20" s="82" t="n"/>
       <c r="C20" s="24" t="n"/>
       <c r="D20" s="24" t="n"/>
       <c r="E20" s="24" t="n"/>
       <c r="F20" s="29" t="n"/>
-      <c r="G20" s="82" t="n"/>
-      <c r="H20" s="82" t="n"/>
-      <c r="I20" s="82" t="n"/>
-      <c r="J20" s="84">
+      <c r="G20" s="81" t="n"/>
+      <c r="H20" s="81" t="n"/>
+      <c r="I20" s="81" t="n"/>
+      <c r="J20" s="83">
         <f>IF(COUNTA(G20:I20)=0,"",SUM(G20:I20))</f>
         <v/>
       </c>
-      <c r="K20" s="86" t="n"/>
+      <c r="K20" s="85" t="n"/>
       <c r="L20" s="24" t="n"/>
       <c r="M20" s="24" t="n"/>
       <c r="N20" s="24" t="n"/>
@@ -8035,19 +8430,19 @@
     </row>
     <row r="21">
       <c r="A21" s="24" t="n"/>
-      <c r="B21" s="83" t="n"/>
+      <c r="B21" s="82" t="n"/>
       <c r="C21" s="24" t="n"/>
       <c r="D21" s="24" t="n"/>
       <c r="E21" s="24" t="n"/>
       <c r="F21" s="29" t="n"/>
-      <c r="G21" s="82" t="n"/>
-      <c r="H21" s="82" t="n"/>
-      <c r="I21" s="82" t="n"/>
-      <c r="J21" s="84">
+      <c r="G21" s="81" t="n"/>
+      <c r="H21" s="81" t="n"/>
+      <c r="I21" s="81" t="n"/>
+      <c r="J21" s="83">
         <f>IF(COUNTA(G21:I21)=0,"",SUM(G21:I21))</f>
         <v/>
       </c>
-      <c r="K21" s="86" t="n"/>
+      <c r="K21" s="85" t="n"/>
       <c r="L21" s="24" t="n"/>
       <c r="M21" s="24" t="n"/>
       <c r="N21" s="24" t="n"/>
@@ -8055,19 +8450,19 @@
     </row>
     <row r="22">
       <c r="A22" s="24" t="n"/>
-      <c r="B22" s="83" t="n"/>
+      <c r="B22" s="82" t="n"/>
       <c r="C22" s="24" t="n"/>
       <c r="D22" s="24" t="n"/>
       <c r="E22" s="24" t="n"/>
       <c r="F22" s="29" t="n"/>
-      <c r="G22" s="82" t="n"/>
-      <c r="H22" s="82" t="n"/>
-      <c r="I22" s="82" t="n"/>
-      <c r="J22" s="84">
+      <c r="G22" s="81" t="n"/>
+      <c r="H22" s="81" t="n"/>
+      <c r="I22" s="81" t="n"/>
+      <c r="J22" s="83">
         <f>IF(COUNTA(G22:I22)=0,"",SUM(G22:I22))</f>
         <v/>
       </c>
-      <c r="K22" s="86" t="n"/>
+      <c r="K22" s="85" t="n"/>
       <c r="L22" s="24" t="n"/>
       <c r="M22" s="24" t="n"/>
       <c r="N22" s="24" t="n"/>
@@ -8075,19 +8470,19 @@
     </row>
     <row r="23">
       <c r="A23" s="24" t="n"/>
-      <c r="B23" s="83" t="n"/>
+      <c r="B23" s="82" t="n"/>
       <c r="C23" s="24" t="n"/>
       <c r="D23" s="24" t="n"/>
       <c r="E23" s="24" t="n"/>
       <c r="F23" s="29" t="n"/>
-      <c r="G23" s="82" t="n"/>
-      <c r="H23" s="82" t="n"/>
-      <c r="I23" s="82" t="n"/>
-      <c r="J23" s="84">
+      <c r="G23" s="81" t="n"/>
+      <c r="H23" s="81" t="n"/>
+      <c r="I23" s="81" t="n"/>
+      <c r="J23" s="83">
         <f>IF(COUNTA(G23:I23)=0,"",SUM(G23:I23))</f>
         <v/>
       </c>
-      <c r="K23" s="86" t="n"/>
+      <c r="K23" s="85" t="n"/>
       <c r="L23" s="24" t="n"/>
       <c r="M23" s="24" t="n"/>
       <c r="N23" s="24" t="n"/>
@@ -8095,19 +8490,19 @@
     </row>
     <row r="24">
       <c r="A24" s="24" t="n"/>
-      <c r="B24" s="83" t="n"/>
+      <c r="B24" s="82" t="n"/>
       <c r="C24" s="24" t="n"/>
       <c r="D24" s="24" t="n"/>
       <c r="E24" s="24" t="n"/>
       <c r="F24" s="29" t="n"/>
-      <c r="G24" s="82" t="n"/>
-      <c r="H24" s="82" t="n"/>
-      <c r="I24" s="82" t="n"/>
-      <c r="J24" s="84">
+      <c r="G24" s="81" t="n"/>
+      <c r="H24" s="81" t="n"/>
+      <c r="I24" s="81" t="n"/>
+      <c r="J24" s="83">
         <f>IF(COUNTA(G24:I24)=0,"",SUM(G24:I24))</f>
         <v/>
       </c>
-      <c r="K24" s="86" t="n"/>
+      <c r="K24" s="85" t="n"/>
       <c r="L24" s="24" t="n"/>
       <c r="M24" s="24" t="n"/>
       <c r="N24" s="24" t="n"/>
@@ -8132,12 +8527,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="14" customWidth="1" style="1" min="1" max="2"/>
     <col width="20" customWidth="1" style="1" min="3" max="9"/>
     <col width="34" customWidth="1" style="1" min="10" max="10"/>
+    <col width="10" customWidth="1" style="1" min="11" max="11"/>
+    <col width="16" customWidth="1" style="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" s="1">
@@ -8159,7 +8556,7 @@
     <row r="2">
       <c r="A2" s="18" t="inlineStr">
         <is>
-          <t>计划人工成本按月度计划人天×自动反算平均人日单价分布。承诺、实际和完工估算需每月更新；空白表示尚无可靠数据。</t>
+          <t>计划人工成本按月度计划人天×自动反算平均人日单价分布。承诺、实际和完工估算需每月更新；空白表示尚无可靠数据。K/L 列实际人天及折算成本自动取自《月度投入明细》实际列，无需手工填写。</t>
         </is>
       </c>
     </row>
@@ -8212,6 +8609,16 @@
       <c r="J4" s="12" t="inlineStr">
         <is>
           <t>偏差说明</t>
+        </is>
+      </c>
+      <c r="K4" s="36" t="inlineStr">
+        <is>
+          <t>实际人天</t>
+        </is>
+      </c>
+      <c r="L4" s="36" t="inlineStr">
+        <is>
+          <t>实际人天折算成本(元)</t>
         </is>
       </c>
     </row>
@@ -8242,6 +8649,14 @@
         <v/>
       </c>
       <c r="J5" s="23" t="n"/>
+      <c r="K5" s="20">
+        <f>月度投入明细!C15</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="20">
+        <f>K5*人工成本预算!$E$3</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="19" t="inlineStr">
@@ -8270,6 +8685,14 @@
         <v/>
       </c>
       <c r="J6" s="23" t="n"/>
+      <c r="K6" s="20">
+        <f>月度投入明细!E15</f>
+        <v>21</v>
+      </c>
+      <c r="L6" s="20">
+        <f>K6*人工成本预算!$E$3</f>
+        <v>29241.2226020511</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
@@ -8298,6 +8721,14 @@
         <v/>
       </c>
       <c r="J7" s="23" t="n"/>
+      <c r="K7" s="20">
+        <f>月度投入明细!G15</f>
+        <v>21</v>
+      </c>
+      <c r="L7" s="20">
+        <f>K7*人工成本预算!$E$3</f>
+        <v>29241.2226020511</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="19" t="inlineStr">
@@ -8326,6 +8757,14 @@
         <v/>
       </c>
       <c r="J8" s="23" t="n"/>
+      <c r="K8" s="20">
+        <f>月度投入明细!I15</f>
+        <v>21</v>
+      </c>
+      <c r="L8" s="20">
+        <f>K8*人工成本预算!$E$3</f>
+        <v>29241.2226020511</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
@@ -8354,6 +8793,14 @@
         <v/>
       </c>
       <c r="J9" s="23" t="n"/>
+      <c r="K9" s="20">
+        <f>月度投入明细!K15</f>
+        <v>63</v>
+      </c>
+      <c r="L9" s="20">
+        <f>K9*人工成本预算!$E$3</f>
+        <v>87723.6678061532</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
@@ -8382,6 +8829,14 @@
         <v/>
       </c>
       <c r="J10" s="23" t="n"/>
+      <c r="K10" s="20">
+        <f>月度投入明细!M15</f>
+        <v>63</v>
+      </c>
+      <c r="L10" s="20">
+        <f>K10*人工成本预算!$E$3</f>
+        <v>87723.6678061532</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
@@ -8410,6 +8865,14 @@
         <v/>
       </c>
       <c r="J11" s="23" t="n"/>
+      <c r="K11" s="20">
+        <f>月度投入明细!O15</f>
+        <v>63</v>
+      </c>
+      <c r="L11" s="20">
+        <f>K11*人工成本预算!$E$3</f>
+        <v>87723.6678061532</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
@@ -8438,6 +8901,14 @@
         <v/>
       </c>
       <c r="J12" s="23" t="n"/>
+      <c r="K12" s="20">
+        <f>月度投入明细!Q15</f>
+        <v>63</v>
+      </c>
+      <c r="L12" s="20">
+        <f>K12*人工成本预算!$E$3</f>
+        <v>87723.6678061532</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
@@ -8466,6 +8937,14 @@
         <v/>
       </c>
       <c r="J13" s="23" t="n"/>
+      <c r="K13" s="20">
+        <f>月度投入明细!S15</f>
+        <v>63</v>
+      </c>
+      <c r="L13" s="20">
+        <f>K13*人工成本预算!$E$3</f>
+        <v>87723.6678061532</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -8494,6 +8973,14 @@
         <v/>
       </c>
       <c r="J14" s="24" t="n"/>
+      <c r="K14" s="20">
+        <f>月度投入明细!U15</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="20">
+        <f>K14*人工成本预算!$E$3</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
@@ -8522,6 +9009,14 @@
         <v/>
       </c>
       <c r="J15" s="24" t="n"/>
+      <c r="K15" s="20">
+        <f>月度投入明细!W15</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="20">
+        <f>K15*人工成本预算!$E$3</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -8550,6 +9045,14 @@
         <v/>
       </c>
       <c r="J16" s="24" t="n"/>
+      <c r="K16" s="20">
+        <f>月度投入明细!Y15</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="20">
+        <f>K16*人工成本预算!$E$3</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
@@ -8578,6 +9081,14 @@
         <v/>
       </c>
       <c r="J17" s="24" t="n"/>
+      <c r="K17" s="20">
+        <f>月度投入明细!AA15</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="20">
+        <f>K17*人工成本预算!$E$3</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
@@ -8606,6 +9117,14 @@
         <v/>
       </c>
       <c r="J18" s="24" t="n"/>
+      <c r="K18" s="20">
+        <f>月度投入明细!AC15</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="20">
+        <f>K18*人工成本预算!$E$3</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
@@ -8634,6 +9153,14 @@
         <v/>
       </c>
       <c r="J19" s="24" t="n"/>
+      <c r="K19" s="20">
+        <f>月度投入明细!AE15</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="20">
+        <f>K19*人工成本预算!$E$3</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
@@ -8662,6 +9189,14 @@
         <v/>
       </c>
       <c r="J20" s="24" t="n"/>
+      <c r="K20" s="20">
+        <f>月度投入明细!AG15</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="20">
+        <f>K20*人工成本预算!$E$3</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
@@ -8690,6 +9225,14 @@
         <v/>
       </c>
       <c r="J21" s="24" t="n"/>
+      <c r="K21" s="20">
+        <f>月度投入明细!AI15</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="20">
+        <f>K21*人工成本预算!$E$3</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
@@ -8718,6 +9261,14 @@
         <v/>
       </c>
       <c r="J22" s="24" t="n"/>
+      <c r="K22" s="20">
+        <f>月度投入明细!AK15</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="20">
+        <f>K22*人工成本预算!$E$3</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
@@ -8746,6 +9297,14 @@
         <v/>
       </c>
       <c r="J23" s="24" t="n"/>
+      <c r="K23" s="20">
+        <f>月度投入明细!AM15</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="20">
+        <f>K23*人工成本预算!$E$3</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
@@ -8774,6 +9333,14 @@
         <v/>
       </c>
       <c r="J24" s="24" t="n"/>
+      <c r="K24" s="20">
+        <f>月度投入明细!AO15</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="20">
+        <f>K24*人工成本预算!$E$3</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="25" t="inlineStr">
@@ -8814,6 +9381,14 @@
         <v/>
       </c>
       <c r="J25" s="25" t="n"/>
+      <c r="K25" s="86">
+        <f>SUM(K5:K24)</f>
+        <v>378</v>
+      </c>
+      <c r="L25" s="86">
+        <f>SUM(L5:L24)</f>
+        <v>526342.006836919</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/合同全生命周期管理系统-项目管理套件/05_成本与合同管理/成本与合同管理-20260918-V5.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/05_成本与合同管理/成本与合同管理-20260918-V5.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="12660"/>
+    <workbookView windowWidth="28260" windowHeight="12660" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="11" r:id="rId1"/>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="B7" s="5">
         <f>人工成本预算!E3</f>
-        <v>1382.27070535903</v>
+        <v>1381.61651658247</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B8" s="5">
         <f>B7/8</f>
-        <v>172.783838169879</v>
+        <v>172.702064572809</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="B9" s="5">
         <f>人工成本预算!D15</f>
-        <v>4721</v>
+        <v>4553</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B10" s="5">
         <f>B7*B9</f>
-        <v>6525700</v>
+        <v>6290500</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="B12" s="5">
         <f>人工成本预算!C15</f>
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3847,17 +3847,17 @@
     <row r="5" spans="1:12">
       <c r="A5" s="5">
         <f>预算基线!J5</f>
-        <v>6525700</v>
+        <v>6290500</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
         <f>人工成本预算!D15</f>
-        <v>4721</v>
+        <v>4553</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5">
         <f>人工成本预算!E3</f>
-        <v>1382.27070535903</v>
+        <v>1381.61651658247</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3">
@@ -4194,26 +4194,26 @@
       </c>
       <c r="E5" s="16" t="str">
         <f>人工成本预算!D15&amp;"人天"</f>
-        <v>4721人天</v>
+        <v>4553人天</v>
       </c>
       <c r="F5" s="49">
         <f>人工成本预算!D15</f>
-        <v>4721</v>
+        <v>4553</v>
       </c>
       <c r="G5" s="50">
         <f>人工成本预算!E3</f>
-        <v>1382.27070535903</v>
+        <v>1381.61651658247</v>
       </c>
       <c r="H5" s="51">
         <f t="shared" ref="H5:H12" si="0">F5*G5</f>
-        <v>6525700</v>
+        <v>6290500</v>
       </c>
       <c r="I5" s="50">
         <v>0</v>
       </c>
       <c r="J5" s="52">
         <f t="shared" ref="J5:J14" si="1">IF(H5="","",H5+I5)</f>
-        <v>6525700</v>
+        <v>6290500</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>75</v>
@@ -4518,14 +4518,14 @@
       <c r="G13" s="53"/>
       <c r="H13" s="54">
         <f>H5*15%</f>
-        <v>978855</v>
+        <v>943575</v>
       </c>
       <c r="I13" s="53">
         <v>0</v>
       </c>
       <c r="J13" s="55">
         <f t="shared" si="1"/>
-        <v>978855</v>
+        <v>943575</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>71</v>
@@ -4557,14 +4557,14 @@
       <c r="G14" s="53"/>
       <c r="H14" s="54">
         <f>H5*15%</f>
-        <v>978855</v>
+        <v>943575</v>
       </c>
       <c r="I14" s="53">
         <v>0</v>
       </c>
       <c r="J14" s="55">
         <f t="shared" si="1"/>
-        <v>978855</v>
+        <v>943575</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>71</v>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="E3" s="37">
         <f>IFERROR(SUM(F5:F14)/SUM(D5:D14),0)</f>
-        <v>1382.27070535903</v>
+        <v>1381.61651658247</v>
       </c>
       <c r="F3" s="38" t="s">
         <v>160</v>
@@ -4818,18 +4818,18 @@
         <v>177</v>
       </c>
       <c r="C11" s="41">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D11" s="42">
         <f>月度投入明细!AP11</f>
-        <v>2075</v>
+        <v>1823</v>
       </c>
       <c r="E11" s="43">
         <v>1300</v>
       </c>
       <c r="F11" s="44">
         <f t="shared" si="0"/>
-        <v>2697500</v>
+        <v>2369900</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>168</v>
@@ -4868,18 +4868,18 @@
         <v>180</v>
       </c>
       <c r="C13" s="41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="42">
         <f>月度投入明细!AP13</f>
-        <v>357</v>
+        <v>441</v>
       </c>
       <c r="E13" s="43">
         <v>1100</v>
       </c>
       <c r="F13" s="44">
         <f t="shared" si="0"/>
-        <v>392700</v>
+        <v>485100</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>168</v>
@@ -4917,19 +4917,19 @@
       <c r="B15" s="45"/>
       <c r="C15" s="46">
         <f>SUM(C5:C14)</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" s="46">
         <f>SUM(D5:D14)</f>
-        <v>4721</v>
+        <v>4553</v>
       </c>
       <c r="E15" s="47">
         <f>$E$3</f>
-        <v>1382.27070535903</v>
+        <v>1381.61651658247</v>
       </c>
       <c r="F15" s="47">
         <f t="shared" si="0"/>
-        <v>6525700</v>
+        <v>6290500</v>
       </c>
       <c r="G15" s="48"/>
     </row>
@@ -6122,37 +6122,37 @@
         <v>0</v>
       </c>
       <c r="V11" s="31">
-        <v>252</v>
+        <v>210</v>
       </c>
       <c r="W11" s="32">
         <v>0</v>
       </c>
-      <c r="X11" s="32">
-        <v>252</v>
+      <c r="X11" s="31">
+        <v>210</v>
       </c>
       <c r="Y11" s="32">
         <v>0</v>
       </c>
-      <c r="Z11" s="32">
-        <v>252</v>
+      <c r="Z11" s="31">
+        <v>210</v>
       </c>
       <c r="AA11" s="32">
         <v>0</v>
       </c>
-      <c r="AB11" s="32">
-        <v>252</v>
+      <c r="AB11" s="31">
+        <v>210</v>
       </c>
       <c r="AC11" s="32">
         <v>0</v>
       </c>
-      <c r="AD11" s="32">
-        <v>252</v>
+      <c r="AD11" s="31">
+        <v>210</v>
       </c>
       <c r="AE11" s="32">
         <v>0</v>
       </c>
-      <c r="AF11" s="32">
-        <v>252</v>
+      <c r="AF11" s="31">
+        <v>210</v>
       </c>
       <c r="AG11" s="32">
         <v>0</v>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="AP11" s="31">
         <f t="shared" si="0"/>
-        <v>2075</v>
+        <v>1823</v>
       </c>
       <c r="AQ11" s="31">
         <f t="shared" si="1"/>
@@ -6191,11 +6191,11 @@
       </c>
       <c r="AR11" s="31">
         <f>人工成本预算!D11</f>
-        <v>2075</v>
+        <v>1823</v>
       </c>
       <c r="AS11" s="31">
         <f t="shared" si="2"/>
-        <v>2075</v>
+        <v>1823</v>
       </c>
       <c r="AT11" s="33">
         <f t="shared" si="3"/>
@@ -6418,25 +6418,25 @@
         <v>0</v>
       </c>
       <c r="X13" s="31">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="Y13" s="32">
         <v>0</v>
       </c>
       <c r="Z13" s="31">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="AA13" s="32">
         <v>0</v>
       </c>
       <c r="AB13" s="31">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="AC13" s="32">
         <v>0</v>
       </c>
       <c r="AD13" s="31">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="AE13" s="32">
         <v>0</v>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="AP13" s="31">
         <f t="shared" si="0"/>
-        <v>357</v>
+        <v>441</v>
       </c>
       <c r="AQ13" s="31">
         <f t="shared" si="1"/>
@@ -6481,11 +6481,11 @@
       </c>
       <c r="AR13" s="31">
         <f>人工成本预算!D13</f>
-        <v>357</v>
+        <v>441</v>
       </c>
       <c r="AS13" s="31">
         <f t="shared" si="2"/>
-        <v>357</v>
+        <v>441</v>
       </c>
       <c r="AT13" s="33">
         <f t="shared" si="3"/>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="V15" s="31">
         <f t="shared" si="4"/>
-        <v>504</v>
+        <v>462</v>
       </c>
       <c r="W15" s="31">
         <f t="shared" si="4"/>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="X15" s="31">
         <f t="shared" si="4"/>
-        <v>504</v>
+        <v>483</v>
       </c>
       <c r="Y15" s="31">
         <f t="shared" si="4"/>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="Z15" s="31">
         <f t="shared" si="4"/>
-        <v>483</v>
+        <v>462</v>
       </c>
       <c r="AA15" s="31">
         <f t="shared" si="4"/>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="AB15" s="31">
         <f t="shared" si="4"/>
-        <v>483</v>
+        <v>462</v>
       </c>
       <c r="AC15" s="31">
         <f t="shared" si="4"/>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AD15" s="31">
         <f t="shared" si="4"/>
-        <v>483</v>
+        <v>462</v>
       </c>
       <c r="AE15" s="31">
         <f t="shared" si="4"/>
@@ -6763,7 +6763,7 @@
       </c>
       <c r="AF15" s="31">
         <f t="shared" si="4"/>
-        <v>483</v>
+        <v>441</v>
       </c>
       <c r="AG15" s="31">
         <f t="shared" si="4"/>
@@ -6803,7 +6803,7 @@
       </c>
       <c r="AP15" s="31">
         <f t="shared" si="4"/>
-        <v>4721</v>
+        <v>4553</v>
       </c>
       <c r="AQ15" s="31">
         <f t="shared" si="4"/>
@@ -6811,15 +6811,15 @@
       </c>
       <c r="AR15" s="31">
         <f t="shared" si="4"/>
-        <v>4721</v>
+        <v>4553</v>
       </c>
       <c r="AS15" s="31">
         <f t="shared" si="2"/>
-        <v>4343</v>
+        <v>4175</v>
       </c>
       <c r="AT15" s="33">
         <f t="shared" si="3"/>
-        <v>0.0800677822495234</v>
+        <v>0.083022183175928</v>
       </c>
     </row>
     <row r="16" ht="17.55" customHeight="1" spans="1:46">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="C6" s="19">
         <f>B6*人工成本预算!$E$3</f>
-        <v>29027.6848125397</v>
+        <v>29013.9468482319</v>
       </c>
       <c r="D6" s="20"/>
       <c r="E6" s="21">
         <f t="shared" si="0"/>
-        <v>29027.6848125397</v>
+        <v>29013.9468482319</v>
       </c>
       <c r="F6" s="20"/>
       <c r="G6" s="20"/>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="L6" s="19">
         <f>K6*人工成本预算!$E$3</f>
-        <v>29027.6848125397</v>
+        <v>29013.9468482319</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="C7" s="19">
         <f>B7*人工成本预算!$E$3</f>
-        <v>29027.6848125397</v>
+        <v>29013.9468482319</v>
       </c>
       <c r="D7" s="20"/>
       <c r="E7" s="21">
         <f t="shared" si="0"/>
-        <v>29027.6848125397</v>
+        <v>29013.9468482319</v>
       </c>
       <c r="F7" s="20"/>
       <c r="G7" s="20"/>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="L7" s="19">
         <f>K7*人工成本预算!$E$3</f>
-        <v>29027.6848125397</v>
+        <v>29013.9468482319</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="C8" s="19">
         <f>B8*人工成本预算!$E$3</f>
-        <v>29027.6848125397</v>
+        <v>29013.9468482319</v>
       </c>
       <c r="D8" s="20"/>
       <c r="E8" s="21">
         <f t="shared" si="0"/>
-        <v>29027.6848125397</v>
+        <v>29013.9468482319</v>
       </c>
       <c r="F8" s="20"/>
       <c r="G8" s="20"/>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="L8" s="19">
         <f>K8*人工成本预算!$E$3</f>
-        <v>29027.6848125397</v>
+        <v>29013.9468482319</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="C9" s="19">
         <f>B9*人工成本预算!$E$3</f>
-        <v>87083.0544376192</v>
+        <v>87041.8405446958</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="21">
         <f t="shared" si="0"/>
-        <v>87083.0544376192</v>
+        <v>87041.8405446958</v>
       </c>
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="L9" s="19">
         <f>K9*人工成本预算!$E$3</f>
-        <v>87083.0544376192</v>
+        <v>87041.8405446958</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="C10" s="19">
         <f>B10*人工成本预算!$E$3</f>
-        <v>87083.0544376192</v>
+        <v>87041.8405446958</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="21">
         <f t="shared" si="0"/>
-        <v>87083.0544376192</v>
+        <v>87041.8405446958</v>
       </c>
       <c r="F10" s="20"/>
       <c r="G10" s="20"/>
@@ -7136,7 +7136,7 @@
       </c>
       <c r="L10" s="19">
         <f>K10*人工成本预算!$E$3</f>
-        <v>87083.0544376192</v>
+        <v>87041.8405446958</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="C11" s="19">
         <f>B11*人工成本预算!$E$3</f>
-        <v>87083.0544376192</v>
+        <v>87041.8405446958</v>
       </c>
       <c r="D11" s="20"/>
       <c r="E11" s="21">
         <f t="shared" si="0"/>
-        <v>87083.0544376192</v>
+        <v>87041.8405446958</v>
       </c>
       <c r="F11" s="20"/>
       <c r="G11" s="20"/>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="L11" s="19">
         <f>K11*人工成本预算!$E$3</f>
-        <v>87083.0544376192</v>
+        <v>87041.8405446958</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="C12" s="19">
         <f>B12*人工成本预算!$E$3</f>
-        <v>87083.0544376192</v>
+        <v>87041.8405446958</v>
       </c>
       <c r="D12" s="20"/>
       <c r="E12" s="21">
         <f t="shared" si="0"/>
-        <v>87083.0544376192</v>
+        <v>87041.8405446958</v>
       </c>
       <c r="F12" s="20"/>
       <c r="G12" s="20"/>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="L12" s="19">
         <f>K12*人工成本预算!$E$3</f>
-        <v>87083.0544376192</v>
+        <v>87041.8405446958</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="C13" s="19">
         <f>B13*人工成本预算!$E$3</f>
-        <v>87083.0544376192</v>
+        <v>87041.8405446958</v>
       </c>
       <c r="D13" s="20"/>
       <c r="E13" s="21">
         <f t="shared" si="0"/>
-        <v>87083.0544376192</v>
+        <v>87041.8405446958</v>
       </c>
       <c r="F13" s="20"/>
       <c r="G13" s="20"/>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="L13" s="19">
         <f>K13*人工成本预算!$E$3</f>
-        <v>87083.0544376192</v>
+        <v>87041.8405446958</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="C14" s="19">
         <f>B14*人工成本预算!$E$3</f>
-        <v>255720.080491421</v>
+        <v>255599.055567758</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="21">
         <f t="shared" si="0"/>
-        <v>255720.080491421</v>
+        <v>255599.055567758</v>
       </c>
       <c r="F14" s="20"/>
       <c r="G14" s="20"/>
@@ -7281,16 +7281,16 @@
       </c>
       <c r="B15" s="5">
         <f>月度投入明细!V15</f>
-        <v>504</v>
+        <v>462</v>
       </c>
       <c r="C15" s="19">
         <f>B15*人工成本预算!$E$3</f>
-        <v>696664.435500953</v>
+        <v>638306.830661103</v>
       </c>
       <c r="D15" s="20"/>
       <c r="E15" s="21">
         <f t="shared" si="0"/>
-        <v>696664.435500953</v>
+        <v>638306.830661103</v>
       </c>
       <c r="F15" s="20"/>
       <c r="G15" s="20"/>
@@ -7315,16 +7315,16 @@
       </c>
       <c r="B16" s="5">
         <f>月度投入明细!X15</f>
-        <v>504</v>
+        <v>483</v>
       </c>
       <c r="C16" s="19">
         <f>B16*人工成本预算!$E$3</f>
-        <v>696664.435500953</v>
+        <v>667320.777509334</v>
       </c>
       <c r="D16" s="20"/>
       <c r="E16" s="21">
         <f t="shared" si="0"/>
-        <v>696664.435500953</v>
+        <v>667320.777509334</v>
       </c>
       <c r="F16" s="20"/>
       <c r="G16" s="20"/>
@@ -7349,16 +7349,16 @@
       </c>
       <c r="B17" s="5">
         <f>月度投入明细!Z15</f>
-        <v>483</v>
+        <v>462</v>
       </c>
       <c r="C17" s="19">
         <f>B17*人工成本预算!$E$3</f>
-        <v>667636.750688414</v>
+        <v>638306.830661103</v>
       </c>
       <c r="D17" s="20"/>
       <c r="E17" s="21">
         <f t="shared" si="0"/>
-        <v>667636.750688414</v>
+        <v>638306.830661103</v>
       </c>
       <c r="F17" s="20"/>
       <c r="G17" s="20"/>
@@ -7383,16 +7383,16 @@
       </c>
       <c r="B18" s="5">
         <f>月度投入明细!AB15</f>
-        <v>483</v>
+        <v>462</v>
       </c>
       <c r="C18" s="19">
         <f>B18*人工成本预算!$E$3</f>
-        <v>667636.750688414</v>
+        <v>638306.830661103</v>
       </c>
       <c r="D18" s="20"/>
       <c r="E18" s="21">
         <f t="shared" si="0"/>
-        <v>667636.750688414</v>
+        <v>638306.830661103</v>
       </c>
       <c r="F18" s="20"/>
       <c r="G18" s="20"/>
@@ -7417,16 +7417,16 @@
       </c>
       <c r="B19" s="5">
         <f>月度投入明细!AD15</f>
-        <v>483</v>
+        <v>462</v>
       </c>
       <c r="C19" s="19">
         <f>B19*人工成本预算!$E$3</f>
-        <v>667636.750688414</v>
+        <v>638306.830661103</v>
       </c>
       <c r="D19" s="20"/>
       <c r="E19" s="21">
         <f t="shared" si="0"/>
-        <v>667636.750688414</v>
+        <v>638306.830661103</v>
       </c>
       <c r="F19" s="20"/>
       <c r="G19" s="20"/>
@@ -7451,16 +7451,16 @@
       </c>
       <c r="B20" s="5">
         <f>月度投入明细!AF15</f>
-        <v>483</v>
+        <v>441</v>
       </c>
       <c r="C20" s="19">
         <f>B20*人工成本预算!$E$3</f>
-        <v>667636.750688414</v>
+        <v>609292.883812871</v>
       </c>
       <c r="D20" s="20"/>
       <c r="E20" s="21">
         <f t="shared" si="0"/>
-        <v>667636.750688414</v>
+        <v>609292.883812871</v>
       </c>
       <c r="F20" s="20"/>
       <c r="G20" s="20"/>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="C21" s="19">
         <f>B21*人工成本预算!$E$3</f>
-        <v>609581.381063334</v>
+        <v>609292.883812871</v>
       </c>
       <c r="D21" s="20"/>
       <c r="E21" s="21">
         <f t="shared" si="0"/>
-        <v>609581.381063334</v>
+        <v>609292.883812871</v>
       </c>
       <c r="F21" s="20"/>
       <c r="G21" s="20"/>
@@ -7523,12 +7523,12 @@
       </c>
       <c r="C22" s="19">
         <f>B22*人工成本预算!$E$3</f>
-        <v>435415.272188096</v>
+        <v>435209.202723479</v>
       </c>
       <c r="D22" s="20"/>
       <c r="E22" s="21">
         <f t="shared" si="0"/>
-        <v>435415.272188096</v>
+        <v>435209.202723479</v>
       </c>
       <c r="F22" s="20"/>
       <c r="G22" s="20"/>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="C23" s="19">
         <f>B23*人工成本预算!$E$3</f>
-        <v>348332.217750477</v>
+        <v>348167.362178783</v>
       </c>
       <c r="D23" s="20"/>
       <c r="E23" s="21">
         <f t="shared" si="0"/>
-        <v>348332.217750477</v>
+        <v>348167.362178783</v>
       </c>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
@@ -7591,12 +7591,12 @@
       </c>
       <c r="C24" s="19">
         <f>B24*人工成本预算!$E$3</f>
-        <v>290276.848125397</v>
+        <v>290139.468482319</v>
       </c>
       <c r="D24" s="20"/>
       <c r="E24" s="21">
         <f t="shared" si="0"/>
-        <v>290276.848125397</v>
+        <v>290139.468482319</v>
       </c>
       <c r="F24" s="20"/>
       <c r="G24" s="20"/>
@@ -7621,11 +7621,11 @@
       </c>
       <c r="B25" s="24">
         <f>SUM(B5:B24)</f>
-        <v>4721</v>
+        <v>4553</v>
       </c>
       <c r="C25" s="24">
         <f>SUM(C5:C24)</f>
-        <v>6525700</v>
+        <v>6290500</v>
       </c>
       <c r="D25" s="24" t="str">
         <f>IF(COUNTA(D5:D24)=0,"",SUM(D5:D24))</f>
@@ -7633,7 +7633,7 @@
       </c>
       <c r="E25" s="25">
         <f>SUM(E5:E24)</f>
-        <v>6525700</v>
+        <v>6290500</v>
       </c>
       <c r="F25" s="24" t="str">
         <f>IF(COUNTA(F5:F24)=0,"",SUM(F5:F24))</f>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="L25" s="26">
         <f>SUM(L5:L24)</f>
-        <v>522498.326625715</v>
+        <v>522251.043268175</v>
       </c>
     </row>
   </sheetData>

--- a/合同全生命周期管理系统-项目管理套件/05_成本与合同管理/成本与合同管理-20260918-V5.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/05_成本与合同管理/成本与合同管理-20260918-V5.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28260" windowHeight="12660" tabRatio="600" firstSheet="0" activeTab="6" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28260" windowHeight="12660" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" state="visible" r:id="rId1"/>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="B5" s="88" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="6">
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>不完整</t>
+          <t>完整（待D-003批准）</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="B19" s="61" t="inlineStr">
         <is>
-          <t>当前只能确认人工成本607.09万元（4,337人天，按角色×月份月度投入明细汇总），不能把该金额视为项目总预算。</t>
+          <t>人工成本607.09万元（4,337人天，按角色×月份月度投入明细汇总）只是项目预算的一部分；十项预算已全量化、合计1,525.22万元（含应急与管理储备各15%），待D-003批准后生效，批准前仍不得视为项目总预算。</t>
         </is>
       </c>
       <c r="C19" s="62" t="n"/>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="31" customHeight="1" s="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>BUD-002</t>
@@ -3823,7 +3823,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="31" customHeight="1" s="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>BUD-003</t>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="31" customHeight="1" s="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>BUD-004</t>
@@ -3964,21 +3964,26 @@
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>环境、存储、备份与容灾</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="n"/>
-      <c r="G9" s="77" t="n"/>
+          <t>PKG-004计划金额（开发/测试/生产/备份容灾资源估算，架构基线后确认）</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="77">
+        <f>采购包计划!H8</f>
+        <v>1800000</v>
+      </c>
       <c r="H9" s="78">
         <f>F9*G9</f>
-        <v>0</v>
+        <v>1800000</v>
       </c>
       <c r="I9" s="77" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="73">
         <f>IF(H9="","",H9+I9)</f>
-        <v>0</v>
+        <v>1800000</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
@@ -3987,7 +3992,7 @@
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>待估算</t>
+          <t>已量化</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -4019,21 +4024,26 @@
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>安全、性能及第三方测评</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="n"/>
-      <c r="G10" s="77" t="n"/>
+          <t>PKG-005计划金额（安全/性能/第三方测评范围估算，测试策略后确认）</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="77">
+        <f>采购包计划!H9</f>
+        <v>180000</v>
+      </c>
       <c r="H10" s="78">
         <f>F10*G10</f>
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="I10" s="77" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="73">
         <f>IF(H10="","",H10+I10)</f>
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
@@ -4042,7 +4052,7 @@
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>待估算</t>
+          <t>已量化</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -4074,21 +4084,26 @@
       </c>
       <c r="E11" s="16" t="inlineStr">
         <is>
-          <t>清洗、转换、迁移和对账</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="77" t="n"/>
+          <t>PKG-006计划金额（存量数据清洗/转换/迁移工作量估算，数据范围后确认）</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="77">
+        <f>采购包计划!H10</f>
+        <v>200000</v>
+      </c>
       <c r="H11" s="78">
         <f>F11*G11</f>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="I11" s="77" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="73">
         <f>IF(H11="","",H11+I11)</f>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
@@ -4097,7 +4112,7 @@
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>待估算</t>
+          <t>已量化</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -4129,21 +4144,26 @@
       </c>
       <c r="E12" s="16" t="inlineStr">
         <is>
-          <t>产品实施、联调与上线保障</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n"/>
-      <c r="G12" s="77" t="n"/>
+          <t>PKG-007计划金额（产品实施/接口支持/上线保障边界估算，合同边界后确认）</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="77">
+        <f>采购包计划!H11</f>
+        <v>160000</v>
+      </c>
       <c r="H12" s="78">
         <f>F12*G12</f>
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="I12" s="77" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="73">
         <f>IF(H12="","",H12+I12)</f>
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
@@ -4152,7 +4172,7 @@
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>待估算</t>
+          <t>已量化</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -4207,7 +4227,7 @@
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>待估算</t>
+          <t>已量化</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -4262,7 +4282,7 @@
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>待估算</t>
+          <t>已量化</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
